--- a/02.descargable/XLSX/01.XLSX correctos/devoluciones.xlsx
+++ b/02.descargable/XLSX/01.XLSX correctos/devoluciones.xlsx
@@ -497,50 +497,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C-001642</t>
+          <t>C-001976</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CL-01427</t>
+          <t>CL-02787</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ET-01642</t>
+          <t>ET-01976</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P-031723</t>
+          <t>P-050733</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PR-00619</t>
+          <t>PR-01420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BR-00031</t>
+          <t>BR-00461</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-000913</t>
+          <t>E-012237</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45742</v>
+        <v>45870</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -552,50 +552,50 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C-004696</t>
+          <t>C-003586</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CL-03466</t>
+          <t>CL-00448</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ET-04696</t>
+          <t>ET-03586</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P-010795</t>
+          <t>P-028946</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PR-01011</t>
+          <t>PR-00319</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BR-00251</t>
+          <t>BR-00065</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-006686</t>
+          <t>E-001888</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45768</v>
+        <v>45844</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -607,50 +607,50 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C-003494</t>
+          <t>C-001757</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CL-00562</t>
+          <t>CL-08551</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ET-03494</t>
+          <t>ET-01757</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P-020096</t>
+          <t>P-039804</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PR-01186</t>
+          <t>PR-00429</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BR-00180</t>
+          <t>BR-00360</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-004798</t>
+          <t>E-009660</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45725</v>
+        <v>45875</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -662,45 +662,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C-003048</t>
+          <t>C-000897</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CL-01502</t>
+          <t>CL-07210</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ET-03048</t>
+          <t>ET-00897</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P-001258</t>
+          <t>P-044929</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PR-00017</t>
+          <t>PR-00513</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BR-00007</t>
+          <t>BR-00057</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>E-000436</t>
+          <t>E-001770</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45730</v>
+        <v>45783</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -717,45 +717,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C-002273</t>
+          <t>C-004344</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CL-07586</t>
+          <t>CL-03354</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ET-02273</t>
+          <t>ET-04344</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P-009203</t>
+          <t>P-045152</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PR-01373</t>
+          <t>PR-01068</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BR-00308</t>
+          <t>BR-00410</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E-008088</t>
+          <t>E-010820</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45840</v>
+        <v>45892</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -772,50 +772,50 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C-003549</t>
+          <t>C-003068</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CL-01301</t>
+          <t>CL-07343</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ET-03549</t>
+          <t>ET-03068</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P-047687</t>
+          <t>P-019869</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PR-00528</t>
+          <t>PR-00197</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BR-00431</t>
+          <t>BR-00334</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E-011414</t>
+          <t>E-008830</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45791</v>
+        <v>45734</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -827,50 +827,50 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C-002694</t>
+          <t>C-000734</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CL-03264</t>
+          <t>CL-06119</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ET-02694</t>
+          <t>ET-00734</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P-049113</t>
+          <t>P-003483</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PR-01013</t>
+          <t>PR-01019</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BR-00447</t>
+          <t>BR-00029</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>E-011647</t>
+          <t>E-000923</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45869</v>
+        <v>45739</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -882,45 +882,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C-001660</t>
+          <t>C-004892</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CL-00940</t>
+          <t>CL-07868</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ET-01660</t>
+          <t>ET-04892</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P-048530</t>
+          <t>P-031982</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PR-00551</t>
+          <t>PR-00373</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BR-00440</t>
+          <t>BR-00289</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E-011574</t>
+          <t>E-007772</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45742</v>
+        <v>45824</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -937,50 +937,50 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C-004185</t>
+          <t>C-000256</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CL-02236</t>
+          <t>CL-09984</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ET-04185</t>
+          <t>ET-00256</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P-004518</t>
+          <t>P-008938</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PR-00696</t>
+          <t>PR-00109</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BR-00040</t>
+          <t>BR-00434</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E-001167</t>
+          <t>E-011586</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45840</v>
+        <v>45837</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -992,50 +992,50 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C-002490</t>
+          <t>C-004941</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CL-06599</t>
+          <t>CL-05015</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ET-02490</t>
+          <t>ET-04941</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P-026458</t>
+          <t>P-018499</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PR-01010</t>
+          <t>PR-00221</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BR-00469</t>
+          <t>BR-00231</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E-012391</t>
+          <t>E-006220</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45784</v>
+        <v>45855</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1047,50 +1047,50 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C-002049</t>
+          <t>C-001397</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CL-06682</t>
+          <t>CL-08907</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ET-02049</t>
+          <t>ET-01397</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P-007297</t>
+          <t>P-009469</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PR-01234</t>
+          <t>PR-01280</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BR-00063</t>
+          <t>BR-00273</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>E-001852</t>
+          <t>E-007388</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45717</v>
+        <v>45733</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1102,50 +1102,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C-000521</t>
+          <t>C-003131</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CL-06898</t>
+          <t>CL-02610</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ET-00521</t>
+          <t>ET-03131</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P-010416</t>
+          <t>P-044826</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PR-01257</t>
+          <t>PR-00783</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BR-00090</t>
+          <t>BR-00317</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>E-002626</t>
+          <t>E-008580</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45771</v>
+        <v>45750</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1157,50 +1157,50 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C-003097</t>
+          <t>C-001862</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CL-02749</t>
+          <t>CL-00422</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ET-03097</t>
+          <t>ET-01862</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P-028965</t>
+          <t>P-044366</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PR-00291</t>
+          <t>PR-00481</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BR-00264</t>
+          <t>BR-00229</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>E-006805</t>
+          <t>E-006018</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45876</v>
+        <v>45839</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1212,50 +1212,50 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C-004888</t>
+          <t>C-004785</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CL-03920</t>
+          <t>CL-00343</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ET-04888</t>
+          <t>ET-04785</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P-053006</t>
+          <t>P-006124</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PR-00730</t>
+          <t>PR-00890</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BR-00326</t>
+          <t>BR-00051</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>E-008605</t>
+          <t>E-001660</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45857</v>
+        <v>45805</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1267,50 +1267,50 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C-000737</t>
+          <t>C-002512</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CL-06650</t>
+          <t>CL-06995</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ET-00737</t>
+          <t>ET-02512</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P-011792</t>
+          <t>P-050987</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PR-00102</t>
+          <t>PR-01303</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BR-00104</t>
+          <t>BR-00463</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>E-002842</t>
+          <t>E-012296</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45825</v>
+        <v>45724</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1322,50 +1322,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C-000139</t>
+          <t>C-004885</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CL-06158</t>
+          <t>CL-04209</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ET-00139</t>
+          <t>ET-04885</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P-035066</t>
+          <t>P-053135</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PR-00411</t>
+          <t>PR-00571</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BR-00316</t>
+          <t>BR-00167</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>E-008423</t>
+          <t>E-004647</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45764</v>
+        <v>45773</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1377,50 +1377,50 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C-002387</t>
+          <t>C-000784</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CL-09560</t>
+          <t>CL-02671</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ET-02387</t>
+          <t>ET-00784</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P-030803</t>
+          <t>P-009555</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PR-00376</t>
+          <t>PR-00132</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BR-00438</t>
+          <t>BR-00018</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>E-011544</t>
+          <t>E-000771</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45738</v>
+        <v>45736</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1432,45 +1432,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C-001678</t>
+          <t>C-003124</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CL-05528</t>
+          <t>CL-00092</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ET-01678</t>
+          <t>ET-03124</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P-024277</t>
+          <t>P-014637</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PR-00971</t>
+          <t>PR-00188</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BR-00219</t>
+          <t>BR-00129</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>E-005781</t>
+          <t>E-003668</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45744</v>
+        <v>45789</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1487,45 +1487,45 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C-002031</t>
+          <t>C-000401</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CL-08118</t>
+          <t>CL-03110</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ET-02031</t>
+          <t>ET-00401</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P-038533</t>
+          <t>P-020615</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PR-00432</t>
+          <t>PR-00223</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BR-00305</t>
+          <t>BR-00047</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>E-007843</t>
+          <t>E-001547</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45879</v>
+        <v>45768</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1542,50 +1542,50 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C-000069</t>
+          <t>C-004963</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CL-00787</t>
+          <t>CL-02982</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ET-00069</t>
+          <t>ET-04963</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P-009486</t>
+          <t>P-030412</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PR-00639</t>
+          <t>PR-00343</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BR-00083</t>
+          <t>BR-00386</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>E-002411</t>
+          <t>E-010318</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45778</v>
+        <v>45826</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1597,45 +1597,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C-003627</t>
+          <t>C-002901</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CL-01671</t>
+          <t>CL-03592</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ET-03627</t>
+          <t>ET-02901</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P-004509</t>
+          <t>P-048571</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PR-00084</t>
+          <t>PR-00528</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BR-00040</t>
+          <t>BR-00125</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>E-001241</t>
+          <t>E-003601</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45741</v>
+        <v>45804</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1652,50 +1652,50 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C-002876</t>
+          <t>C-004072</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CL-08450</t>
+          <t>CL-04191</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ET-02876</t>
+          <t>ET-04072</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P-046375</t>
+          <t>P-010908</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PR-01163</t>
+          <t>PR-00127</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BR-00422</t>
+          <t>BR-00025</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>E-011065</t>
+          <t>E-000894</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45872</v>
+        <v>45870</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1707,50 +1707,50 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C-004655</t>
+          <t>C-002180</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CL-09975</t>
+          <t>CL-07361</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ET-04655</t>
+          <t>ET-02180</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P-016574</t>
+          <t>P-005533</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PR-00855</t>
+          <t>PR-00062</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BR-00151</t>
+          <t>BR-00046</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>E-003874</t>
+          <t>E-001518</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45812</v>
+        <v>45845</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1762,45 +1762,45 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C-003661</t>
+          <t>C-003243</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CL-02558</t>
+          <t>CL-08041</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ET-03661</t>
+          <t>ET-03243</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P-046195</t>
+          <t>P-023952</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PR-00547</t>
+          <t>PR-00269</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BR-00386</t>
+          <t>BR-00215</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>E-010183</t>
+          <t>E-005822</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45781</v>
+        <v>45879</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1817,41 +1817,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C-003114</t>
+          <t>C-000836</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CL-01422</t>
+          <t>CL-01303</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ET-03114</t>
+          <t>ET-00836</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P-026560</t>
+          <t>P-011548</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PR-00317</t>
+          <t>PR-00101</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BR-00238</t>
+          <t>BR-00465</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>E-006430</t>
+          <t>E-012384</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45723</v>
+        <v>45802</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1872,50 +1872,50 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C-002153</t>
+          <t>C-002313</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CL-04418</t>
+          <t>CL-04293</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ET-02153</t>
+          <t>ET-02313</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P-044621</t>
+          <t>P-020370</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PR-00506</t>
+          <t>PR-00232</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BR-00215</t>
+          <t>BR-00184</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>E-005742</t>
+          <t>E-004873</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45870</v>
+        <v>45755</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1927,50 +1927,50 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C-004146</t>
+          <t>C-000835</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CL-03881</t>
+          <t>CL-02383</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ET-04146</t>
+          <t>ET-00835</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P-023082</t>
+          <t>P-028206</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PR-00241</t>
+          <t>PR-00288</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BR-00024</t>
+          <t>BR-00011</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>E-000842</t>
+          <t>E-000634</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45845</v>
+        <v>45826</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1982,50 +1982,50 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C-000860</t>
+          <t>C-000047</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CL-08617</t>
+          <t>CL-05928</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ET-00860</t>
+          <t>ET-00047</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P-011716</t>
+          <t>P-026146</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PR-00102</t>
+          <t>PR-00295</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BR-00103</t>
+          <t>BR-00273</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>E-002835</t>
+          <t>E-007384</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45853</v>
+        <v>45801</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2037,50 +2037,50 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C-001640</t>
+          <t>C-000156</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CL-07113</t>
+          <t>CL-08931</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ET-01640</t>
+          <t>ET-00156</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P-037218</t>
+          <t>P-003347</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PR-00383</t>
+          <t>PR-00009</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BR-00340</t>
+          <t>BR-00027</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>E-008728</t>
+          <t>E-000913</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45822</v>
+        <v>45865</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2092,50 +2092,50 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C-001550</t>
+          <t>C-003933</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CL-00766</t>
+          <t>CL-05862</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ET-01550</t>
+          <t>ET-03933</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P-028346</t>
+          <t>P-049174</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PR-00290</t>
+          <t>PR-00561</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BR-00256</t>
+          <t>BR-00448</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>E-006752</t>
+          <t>E-011785</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45846</v>
+        <v>45713</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2147,50 +2147,50 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C-002477</t>
+          <t>C-001118</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CL-06109</t>
+          <t>CL-05463</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ET-02477</t>
+          <t>ET-01118</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P-002550</t>
+          <t>P-012725</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PR-00006</t>
+          <t>PR-00919</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BR-00019</t>
+          <t>BR-00439</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>E-000760</t>
+          <t>E-011675</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45724</v>
+        <v>45823</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2202,50 +2202,50 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C-000598</t>
+          <t>C-000170</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CL-07489</t>
+          <t>CL-03882</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ET-00598</t>
+          <t>ET-00170</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P-036506</t>
+          <t>P-027122</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PR-00412</t>
+          <t>PR-00732</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BR-00237</t>
+          <t>BR-00041</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>E-006424</t>
+          <t>E-001287</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45777</v>
+        <v>45854</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2257,50 +2257,50 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C-002744</t>
+          <t>C-001572</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CL-04319</t>
+          <t>CL-07339</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ET-02744</t>
+          <t>ET-01572</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P-018181</t>
+          <t>P-009820</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PR-00816</t>
+          <t>PR-01493</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BR-00385</t>
+          <t>BR-00085</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>E-010149</t>
+          <t>E-002547</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45715</v>
+        <v>45822</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2312,45 +2312,45 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C-002986</t>
+          <t>C-004499</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CL-07392</t>
+          <t>CL-04221</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ET-02986</t>
+          <t>ET-04499</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P-007646</t>
+          <t>P-052105</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PR-00084</t>
+          <t>PR-00575</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BR-00067</t>
+          <t>BR-00215</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>E-001878</t>
+          <t>E-005825</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45743</v>
+        <v>45793</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2367,45 +2367,45 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C-003898</t>
+          <t>C-000106</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CL-01648</t>
+          <t>CL-09154</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ET-03898</t>
+          <t>ET-00106</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P-041718</t>
+          <t>P-000962</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PR-00475</t>
+          <t>PR-01078</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BR-00192</t>
+          <t>BR-00305</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>E-005100</t>
+          <t>E-007928</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45802</v>
+        <v>45794</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2422,50 +2422,50 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C-001606</t>
+          <t>C-004715</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CL-05887</t>
+          <t>CL-01087</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ET-01606</t>
+          <t>ET-04715</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P-006229</t>
+          <t>P-047007</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PR-00856</t>
+          <t>PR-01134</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BR-00052</t>
+          <t>BR-00426</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>E-001654</t>
+          <t>E-011365</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45777</v>
+        <v>45847</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2477,50 +2477,50 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C-004396</t>
+          <t>C-002085</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CL-01697</t>
+          <t>CL-04442</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ET-04396</t>
+          <t>ET-02085</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P-043981</t>
+          <t>P-026895</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PR-01232</t>
+          <t>PR-00315</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>BR-00376</t>
+          <t>BR-00241</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>E-009720</t>
+          <t>E-006613</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45784</v>
+        <v>45811</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2532,50 +2532,50 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>C-002717</t>
+          <t>C-001912</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CL-02019</t>
+          <t>CL-02994</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ET-02717</t>
+          <t>ET-01912</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P-044957</t>
+          <t>P-006109</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PR-00503</t>
+          <t>PR-01478</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>BR-00408</t>
+          <t>BR-00051</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>E-010645</t>
+          <t>E-001661</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45881</v>
+        <v>45796</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2587,45 +2587,45 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C-002490</t>
+          <t>C-003293</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CL-06599</t>
+          <t>CL-04729</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ET-02490</t>
+          <t>ET-03293</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P-051783</t>
+          <t>P-013850</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PR-00776</t>
+          <t>PR-00154</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BR-00469</t>
+          <t>BR-00122</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>E-012391</t>
+          <t>E-003461</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45822</v>
+        <v>45796</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2642,50 +2642,50 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C-004270</t>
+          <t>C-002505</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CL-01394</t>
+          <t>CL-01145</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ET-04270</t>
+          <t>ET-02505</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P-040285</t>
+          <t>P-036842</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PR-00470</t>
+          <t>PR-00740</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>BR-00365</t>
+          <t>BR-00335</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>E-009623</t>
+          <t>E-008835</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45742</v>
+        <v>45795</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2697,50 +2697,50 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C-001324</t>
+          <t>C-001640</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CL-05963</t>
+          <t>CL-04100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ET-01324</t>
+          <t>ET-01640</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P-053362</t>
+          <t>P-031025</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PR-01285</t>
+          <t>PR-00335</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>BR-00486</t>
+          <t>BR-00279</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>E-012628</t>
+          <t>E-007597</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45776</v>
+        <v>45834</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2752,45 +2752,45 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C-000270</t>
+          <t>C-003505</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CL-09067</t>
+          <t>CL-04253</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ET-00270</t>
+          <t>ET-03505</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P-030712</t>
+          <t>P-016869</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PR-00341</t>
+          <t>PR-01263</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BR-00276</t>
+          <t>BR-00223</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>E-007415</t>
+          <t>E-005887</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45848</v>
+        <v>45884</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2807,27 +2807,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C-002914</t>
+          <t>C-003651</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CL-04652</t>
+          <t>CL-03892</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ET-02914</t>
+          <t>ET-03651</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P-025447</t>
+          <t>P-027490</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PR-01379</t>
+          <t>PR-01015</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2837,15 +2837,15 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>E-006040</t>
+          <t>E-006131</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45826</v>
+        <v>45711</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2862,50 +2862,50 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C-004284</t>
+          <t>C-000780</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CL-04711</t>
+          <t>CL-09305</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ET-04284</t>
+          <t>ET-00780</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P-046403</t>
+          <t>P-012247</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PR-01274</t>
+          <t>PR-01479</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BR-00422</t>
+          <t>BR-00329</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>E-011101</t>
+          <t>E-008781</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45862</v>
+        <v>45732</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2917,50 +2917,50 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C-001531</t>
+          <t>C-004300</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CL-05513</t>
+          <t>CL-06032</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ET-01531</t>
+          <t>ET-04300</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P-004341</t>
+          <t>P-050926</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PR-01231</t>
+          <t>PR-00606</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BR-00427</t>
+          <t>BR-00462</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>E-011323</t>
+          <t>E-012286</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45771</v>
+        <v>45723</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2972,50 +2972,50 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C-000853</t>
+          <t>C-002082</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CL-06412</t>
+          <t>CL-01608</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ET-00853</t>
+          <t>ET-02082</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P-051767</t>
+          <t>P-030279</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PR-01414</t>
+          <t>PR-00929</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BR-00469</t>
+          <t>BR-00419</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>E-012389</t>
+          <t>E-010922</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45780</v>
+        <v>45783</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3027,45 +3027,45 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C-000072</t>
+          <t>C-000245</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CL-05237</t>
+          <t>CL-07335</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ET-00072</t>
+          <t>ET-00245</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P-010594</t>
+          <t>P-010844</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PR-01011</t>
+          <t>PR-00963</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>BR-00092</t>
+          <t>BR-00094</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>E-002670</t>
+          <t>E-002738</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45811</v>
+        <v>45746</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3082,50 +3082,50 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C-000034</t>
+          <t>C-001118</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CL-05705</t>
+          <t>CL-05463</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ET-00034</t>
+          <t>ET-01118</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P-019922</t>
+          <t>P-018748</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PR-01250</t>
+          <t>PR-00983</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BR-00178</t>
+          <t>BR-00439</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>E-004784</t>
+          <t>E-011675</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45846</v>
+        <v>45883</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -3137,50 +3137,50 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C-000610</t>
+          <t>C-003095</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CL-08420</t>
+          <t>CL-02551</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ET-00610</t>
+          <t>ET-03095</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P-032725</t>
+          <t>P-007017</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PR-00827</t>
+          <t>PR-01181</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>BR-00043</t>
+          <t>BR-00060</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>E-001335</t>
+          <t>E-001813</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45808</v>
+        <v>45821</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3192,50 +3192,50 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C-001359</t>
+          <t>C-003581</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CL-06275</t>
+          <t>CL-06417</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ET-01359</t>
+          <t>ET-03581</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P-013040</t>
+          <t>P-019445</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PR-00186</t>
+          <t>PR-01136</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>BR-00317</t>
+          <t>BR-00173</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>E-008455</t>
+          <t>E-004757</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45850</v>
+        <v>45798</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3247,50 +3247,50 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C-002158</t>
+          <t>C-000475</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CL-00605</t>
+          <t>CL-00966</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ET-02158</t>
+          <t>ET-00475</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P-031426</t>
+          <t>P-027939</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PR-00619</t>
+          <t>PR-00294</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BR-00283</t>
+          <t>BR-00251</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>E-007559</t>
+          <t>E-006775</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45890</v>
+        <v>45820</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3302,50 +3302,50 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C-004406</t>
+          <t>C-001178</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CL-04800</t>
+          <t>CL-06113</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ET-04406</t>
+          <t>ET-01178</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P-044394</t>
+          <t>P-041252</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PR-01058</t>
+          <t>PR-00840</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>BR-00375</t>
+          <t>BR-00377</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>E-009712</t>
+          <t>E-009855</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45835</v>
+        <v>45849</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -3357,45 +3357,45 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C-003948</t>
+          <t>C-002508</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CL-04571</t>
+          <t>CL-06057</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ET-03948</t>
+          <t>ET-02508</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P-009240</t>
+          <t>P-022627</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PR-01390</t>
+          <t>PR-01039</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>BR-00081</t>
+          <t>BR-00343</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>E-002304</t>
+          <t>E-008891</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45731</v>
+        <v>45732</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3412,50 +3412,50 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C-004230</t>
+          <t>C-001480</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CL-04464</t>
+          <t>CL-08062</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ET-04230</t>
+          <t>ET-01480</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P-027774</t>
+          <t>P-006101</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PR-00327</t>
+          <t>PR-00081</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>BR-00250</t>
+          <t>BR-00019</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>E-006675</t>
+          <t>E-000795</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45744</v>
+        <v>45768</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -3467,41 +3467,41 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C-003209</t>
+          <t>C-001106</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CL-00231</t>
+          <t>CL-04970</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ET-03209</t>
+          <t>ET-01106</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P-016393</t>
+          <t>P-029598</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PR-00147</t>
+          <t>PR-01190</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>BR-00230</t>
+          <t>BR-00269</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>E-005979</t>
+          <t>E-007203</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45863</v>
+        <v>45855</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3522,50 +3522,50 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C-003235</t>
+          <t>C-000700</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CL-03886</t>
+          <t>CL-06106</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ET-03235</t>
+          <t>ET-00700</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P-037961</t>
+          <t>P-030709</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PR-00461</t>
+          <t>PR-00340</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>BR-00345</t>
+          <t>BR-00213</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>E-009058</t>
+          <t>E-005797</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45837</v>
+        <v>45748</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3577,45 +3577,45 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C-000846</t>
+          <t>C-002079</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CL-05448</t>
+          <t>CL-05060</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ET-00846</t>
+          <t>ET-02079</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P-044813</t>
+          <t>P-047026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PR-00505</t>
+          <t>PR-00525</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>BR-00406</t>
+          <t>BR-00128</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>E-010629</t>
+          <t>E-003659</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45817</v>
+        <v>45888</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3632,50 +3632,50 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C-002820</t>
+          <t>C-002330</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CL-06238</t>
+          <t>CL-05187</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ET-02820</t>
+          <t>ET-02330</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P-043685</t>
+          <t>P-003629</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PR-00517</t>
+          <t>PR-01019</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BR-00250</t>
+          <t>BR-00031</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>E-006673</t>
+          <t>E-000937</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45727</v>
+        <v>45758</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3687,45 +3687,45 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C-000688</t>
+          <t>C-004928</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CL-02178</t>
+          <t>CL-05381</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ET-00688</t>
+          <t>ET-04928</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P-017546</t>
+          <t>P-012277</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PR-01396</t>
+          <t>PR-00127</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>BR-00157</t>
+          <t>BR-00458</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>E-004283</t>
+          <t>E-012106</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45797</v>
+        <v>45718</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3742,50 +3742,50 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C-000424</t>
+          <t>C-002313</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CL-02362</t>
+          <t>CL-04293</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ET-00424</t>
+          <t>ET-02313</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P-027165</t>
+          <t>P-019690</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PR-00295</t>
+          <t>PR-01298</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BR-00243</t>
+          <t>BR-00184</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>E-006563</t>
+          <t>E-004873</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45847</v>
+        <v>45884</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3797,50 +3797,50 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C-002735</t>
+          <t>C-004958</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CL-04618</t>
+          <t>CL-02808</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ET-02735</t>
+          <t>ET-04958</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P-041767</t>
+          <t>P-037790</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PR-00499</t>
+          <t>PR-01223</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BR-00123</t>
+          <t>BR-00052</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>E-003492</t>
+          <t>E-001677</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45871</v>
+        <v>45800</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3852,45 +3852,45 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C-002415</t>
+          <t>C-000963</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CL-07647</t>
+          <t>CL-02726</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ET-02415</t>
+          <t>ET-00963</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P-016700</t>
+          <t>P-046996</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PR-00862</t>
+          <t>PR-00551</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BR-00152</t>
+          <t>BR-00426</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>E-003881</t>
+          <t>E-011397</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45814</v>
+        <v>45835</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3907,41 +3907,41 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C-002134</t>
+          <t>C-001317</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CL-05937</t>
+          <t>CL-01665</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ET-02134</t>
+          <t>ET-01317</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P-035326</t>
+          <t>P-023208</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PR-00388</t>
+          <t>PR-00247</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>BR-00008</t>
+          <t>BR-00207</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>E-000480</t>
+          <t>E-005688</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45756</v>
+        <v>45772</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3962,50 +3962,50 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C-000546</t>
+          <t>C-000862</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CL-08001</t>
+          <t>CL-05228</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ET-00546</t>
+          <t>ET-00862</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P-035609</t>
+          <t>P-007412</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PR-01048</t>
+          <t>PR-00083</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>BR-00456</t>
+          <t>BR-00082</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>E-011709</t>
+          <t>E-002411</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45805</v>
+        <v>45867</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4017,45 +4017,45 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C-004704</t>
+          <t>C-002313</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CL-03478</t>
+          <t>CL-04293</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ET-04704</t>
+          <t>ET-02313</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P-018494</t>
+          <t>P-020370</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PR-00235</t>
+          <t>PR-00232</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BR-00179</t>
+          <t>BR-00184</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>E-004788</t>
+          <t>E-004873</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45781</v>
+        <v>45794</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4072,41 +4072,41 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C-002497</t>
+          <t>C-002645</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CL-03825</t>
+          <t>CL-01529</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ET-02497</t>
+          <t>ET-02645</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P-008292</t>
+          <t>P-010164</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PR-00094</t>
+          <t>PR-00141</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>BR-00076</t>
+          <t>BR-00088</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>E-001935</t>
+          <t>E-002635</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45868</v>
+        <v>45801</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -4127,50 +4127,50 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C-001200</t>
+          <t>C-003339</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CL-01603</t>
+          <t>CL-05229</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ET-01200</t>
+          <t>ET-03339</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P-048369</t>
+          <t>P-034583</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PR-00528</t>
+          <t>PR-01385</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BR-00319</t>
+          <t>BR-00312</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>E-008482</t>
+          <t>E-008408</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45717</v>
+        <v>45840</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4182,50 +4182,50 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C-004235</t>
+          <t>C-004722</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CL-06109</t>
+          <t>CL-04621</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ET-04235</t>
+          <t>ET-04722</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P-048654</t>
+          <t>P-013081</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PR-00525</t>
+          <t>PR-00828</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BR-00441</t>
+          <t>BR-00117</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>E-011586</t>
+          <t>E-003260</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45748</v>
+        <v>45731</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -4237,50 +4237,50 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C-001283</t>
+          <t>C-001433</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CL-00656</t>
+          <t>CL-09698</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ET-01283</t>
+          <t>ET-01433</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P-027399</t>
+          <t>P-023702</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PR-00329</t>
+          <t>PR-00994</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BR-00246</t>
+          <t>BR-00212</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>E-006614</t>
+          <t>E-005771</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45821</v>
+        <v>45727</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4292,50 +4292,50 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>C-002220</t>
+          <t>C-004000</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CL-01301</t>
+          <t>CL-05187</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ET-02220</t>
+          <t>ET-04000</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P-033758</t>
+          <t>P-019398</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PR-00382</t>
+          <t>PR-00232</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BR-00480</t>
+          <t>BR-00314</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>E-012571</t>
+          <t>E-008539</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45876</v>
+        <v>45793</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4347,50 +4347,50 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C-002236</t>
+          <t>C-000199</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CL-05306</t>
+          <t>CL-02266</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ET-02236</t>
+          <t>ET-00199</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P-013360</t>
+          <t>P-024747</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PR-00178</t>
+          <t>PR-01254</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>BR-00119</t>
+          <t>BR-00225</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>E-003296</t>
+          <t>E-005901</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45765</v>
+        <v>45887</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4402,50 +4402,50 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C-001142</t>
+          <t>C-000269</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CL-01722</t>
+          <t>CL-02691</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ET-01142</t>
+          <t>ET-00269</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P-035138</t>
+          <t>P-027181</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PR-00419</t>
+          <t>PR-00898</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>BR-00346</t>
+          <t>BR-00244</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>E-009093</t>
+          <t>E-006656</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45813</v>
+        <v>45772</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4457,50 +4457,50 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C-002654</t>
+          <t>C-001016</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CL-02252</t>
+          <t>CL-07493</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ET-02654</t>
+          <t>ET-01016</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P-002969</t>
+          <t>P-027873</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PR-00008</t>
+          <t>PR-01015</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>BR-00287</t>
+          <t>BR-00273</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>E-007622</t>
+          <t>E-007401</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45849</v>
+        <v>45769</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -4512,45 +4512,45 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C-000407</t>
+          <t>C-003311</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CL-08241</t>
+          <t>CL-09873</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ET-00407</t>
+          <t>ET-03311</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P-001203</t>
+          <t>P-029336</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PR-01262</t>
+          <t>PR-00357</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>BR-00007</t>
+          <t>BR-00180</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>E-000445</t>
+          <t>E-004846</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45881</v>
+        <v>45795</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4567,50 +4567,50 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C-001137</t>
+          <t>C-003897</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CL-04851</t>
+          <t>CL-05317</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ET-01137</t>
+          <t>ET-03897</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P-002395</t>
+          <t>P-003552</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PR-01459</t>
+          <t>PR-00035</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BR-00018</t>
+          <t>BR-00030</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>E-000752</t>
+          <t>E-000928</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45792</v>
+        <v>45726</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4622,50 +4622,50 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C-003965</t>
+          <t>C-001344</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CL-08722</t>
+          <t>CL-07678</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ET-03965</t>
+          <t>ET-01344</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P-010482</t>
+          <t>P-047631</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PR-00139</t>
+          <t>PR-00563</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>BR-00171</t>
+          <t>BR-00431</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>E-004667</t>
+          <t>E-011537</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45797</v>
+        <v>45887</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4677,45 +4677,45 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C-002820</t>
+          <t>C-001911</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CL-06238</t>
+          <t>CL-09163</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ET-02820</t>
+          <t>ET-01911</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P-017391</t>
+          <t>P-028145</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PR-00845</t>
+          <t>PR-01120</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>BR-00250</t>
+          <t>BR-00231</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>E-006673</t>
+          <t>E-006211</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45871</v>
+        <v>45765</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4732,50 +4732,50 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C-001920</t>
+          <t>C-004665</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CL-04690</t>
+          <t>CL-06162</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ET-01920</t>
+          <t>ET-04665</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P-010617</t>
+          <t>P-050485</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PR-01139</t>
+          <t>PR-00583</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>BR-00092</t>
+          <t>BR-00459</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>E-002656</t>
+          <t>E-012162</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45769</v>
+        <v>45775</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4787,50 +4787,50 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C-003272</t>
+          <t>C-000586</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CL-03040</t>
+          <t>CL-01412</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ET-03272</t>
+          <t>ET-00586</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P-014676</t>
+          <t>P-049497</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PR-00147</t>
+          <t>PR-00550</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BR-00129</t>
+          <t>BR-00452</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>E-003622</t>
+          <t>E-011816</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45865</v>
+        <v>45863</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4842,45 +4842,45 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C-002134</t>
+          <t>C-002019</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CL-05937</t>
+          <t>CL-09953</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ET-02134</t>
+          <t>ET-02019</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P-035326</t>
+          <t>P-033062</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PR-00388</t>
+          <t>PR-00982</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BR-00008</t>
+          <t>BR-00373</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>E-000480</t>
+          <t>E-009828</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45740</v>
+        <v>45825</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4897,45 +4897,45 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>C-004151</t>
+          <t>C-002957</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CL-03418</t>
+          <t>CL-01457</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ET-04151</t>
+          <t>ET-02957</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P-035923</t>
+          <t>P-033846</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PR-01104</t>
+          <t>PR-00395</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>BR-00324</t>
+          <t>BR-00196</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>E-008573</t>
+          <t>E-005328</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45863</v>
+        <v>45824</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4952,50 +4952,50 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>C-003385</t>
+          <t>C-002758</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CL-08818</t>
+          <t>CL-02225</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ET-03385</t>
+          <t>ET-02758</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P-006413</t>
+          <t>P-009674</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PR-01355</t>
+          <t>PR-00623</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>BR-00021</t>
+          <t>BR-00084</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>E-000804</t>
+          <t>E-002497</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45793</v>
+        <v>45889</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5007,50 +5007,50 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>C-003575</t>
+          <t>C-004205</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CL-02159</t>
+          <t>CL-01490</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ET-03575</t>
+          <t>ET-04205</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P-044819</t>
+          <t>P-035948</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PR-00506</t>
+          <t>PR-00886</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BR-00406</t>
+          <t>BR-00325</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>E-010629</t>
+          <t>E-008728</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45829</v>
+        <v>45787</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5062,45 +5062,45 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C-003702</t>
+          <t>C-001412</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CL-03021</t>
+          <t>CL-09310</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ET-03702</t>
+          <t>ET-01412</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P-027270</t>
+          <t>P-046946</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PR-00690</t>
+          <t>PR-00638</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>BR-00244</t>
+          <t>BR-00425</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>E-006574</t>
+          <t>E-011343</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45744</v>
+        <v>45719</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5117,50 +5117,50 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C-001410</t>
+          <t>C-002603</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CL-03277</t>
+          <t>CL-07598</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ET-01410</t>
+          <t>ET-02603</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P-036926</t>
+          <t>P-049197</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PR-00412</t>
+          <t>PR-00550</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>BR-00016</t>
+          <t>BR-00364</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>E-000716</t>
+          <t>E-009730</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45755</v>
+        <v>45722</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -5172,50 +5172,50 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>C-001357</t>
+          <t>C-002834</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CL-04888</t>
+          <t>CL-05737</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ET-01357</t>
+          <t>ET-02834</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P-029723</t>
+          <t>P-016290</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PR-00348</t>
+          <t>PR-00188</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BR-00269</t>
+          <t>BR-00274</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>E-007119</t>
+          <t>E-007452</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45892</v>
+        <v>45822</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5227,45 +5227,45 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C-001589</t>
+          <t>C-002328</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CL-04650</t>
+          <t>CL-05168</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ET-01589</t>
+          <t>ET-02328</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P-044403</t>
+          <t>P-005652</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PR-00515</t>
+          <t>PR-01181</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>BR-00407</t>
+          <t>BR-00190</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>E-010636</t>
+          <t>E-004912</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45850</v>
+        <v>45756</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5282,45 +5282,45 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>C-000662</t>
+          <t>C-004955</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CL-03298</t>
+          <t>CL-02521</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ET-00662</t>
+          <t>ET-04955</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P-045538</t>
+          <t>P-027379</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PR-00517</t>
+          <t>PR-01120</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>BR-00416</t>
+          <t>BR-00245</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>E-010699</t>
+          <t>E-006686</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45837</v>
+        <v>45804</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5337,50 +5337,50 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C-000557</t>
+          <t>C-004075</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CL-04930</t>
+          <t>CL-05113</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ET-00557</t>
+          <t>ET-04075</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P-023521</t>
+          <t>P-045694</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PR-00250</t>
+          <t>PR-00504</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BR-00210</t>
+          <t>BR-00194</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>E-005659</t>
+          <t>E-005263</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45854</v>
+        <v>45746</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -5392,50 +5392,50 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>C-003965</t>
+          <t>C-001178</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CL-08722</t>
+          <t>CL-06113</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ET-03965</t>
+          <t>ET-01178</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P-035605</t>
+          <t>P-041252</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PR-00383</t>
+          <t>PR-00840</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>BR-00171</t>
+          <t>BR-00377</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>E-004667</t>
+          <t>E-009855</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>45863</v>
+        <v>45712</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5447,45 +5447,45 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C-003710</t>
+          <t>C-003726</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CL-06527</t>
+          <t>CL-01746</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ET-03710</t>
+          <t>ET-03726</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P-039644</t>
+          <t>P-033410</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PR-00436</t>
+          <t>PR-00381</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>BR-00358</t>
+          <t>BR-00353</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>E-009492</t>
+          <t>E-009539</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45840</v>
+        <v>45740</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5502,45 +5502,45 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C-004216</t>
+          <t>C-004082</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CL-01404</t>
+          <t>CL-05876</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ET-04216</t>
+          <t>ET-04082</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P-038085</t>
+          <t>P-018261</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PR-00434</t>
+          <t>PR-01433</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>BR-00260</t>
+          <t>BR-00361</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>E-006775</t>
+          <t>E-009674</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>45726</v>
+        <v>45884</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5557,45 +5557,45 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>C-002048</t>
+          <t>C-001448</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CL-00982</t>
+          <t>CL-05632</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ET-02048</t>
+          <t>ET-01448</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P-009708</t>
+          <t>P-014382</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PR-00614</t>
+          <t>PR-00151</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>BR-00407</t>
+          <t>BR-00126</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>E-010637</t>
+          <t>E-003614</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5612,50 +5612,50 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C-004833</t>
+          <t>C-003259</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CL-09410</t>
+          <t>CL-05832</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ET-04833</t>
+          <t>ET-03259</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P-001454</t>
+          <t>P-031758</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PR-01147</t>
+          <t>PR-00993</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BR-00321</t>
+          <t>BR-00194</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>E-008511</t>
+          <t>E-005245</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>45727</v>
+        <v>45760</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5667,50 +5667,50 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C-001881</t>
+          <t>C-002389</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CL-04248</t>
+          <t>CL-07112</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ET-01881</t>
+          <t>ET-02389</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P-029407</t>
+          <t>P-012428</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PR-00336</t>
+          <t>PR-01280</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BR-00268</t>
+          <t>BR-00472</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>E-006987</t>
+          <t>E-012564</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>45875</v>
+        <v>45806</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -5722,45 +5722,45 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>C-004368</t>
+          <t>C-001607</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CL-03080</t>
+          <t>CL-00270</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ET-04368</t>
+          <t>ET-01607</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P-000208</t>
+          <t>P-050245</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PR-00027</t>
+          <t>PR-00984</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>BR-00139</t>
+          <t>BR-00458</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>E-003795</t>
+          <t>E-012017</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>45765</v>
+        <v>45823</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5777,41 +5777,41 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>C-004939</t>
+          <t>C-004162</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CL-05503</t>
+          <t>CL-07648</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ET-04939</t>
+          <t>ET-04162</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P-028310</t>
+          <t>P-039301</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PR-00315</t>
+          <t>PR-00457</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>BR-00030</t>
+          <t>BR-00183</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>E-000906</t>
+          <t>E-004867</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45763</v>
+        <v>45793</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -5832,45 +5832,45 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C-003175</t>
+          <t>C-000562</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CL-07549</t>
+          <t>CL-04544</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ET-03175</t>
+          <t>ET-00562</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P-020149</t>
+          <t>P-045846</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PR-00232</t>
+          <t>PR-00741</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BR-00058</t>
+          <t>BR-00419</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>E-001758</t>
+          <t>E-010910</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>45814</v>
+        <v>45809</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5887,45 +5887,45 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>C-003838</t>
+          <t>C-002505</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CL-09293</t>
+          <t>CL-01145</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ET-03838</t>
+          <t>ET-02505</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P-015197</t>
+          <t>P-036842</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PR-00149</t>
+          <t>PR-00740</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>BR-00276</t>
+          <t>BR-00335</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>E-007428</t>
+          <t>E-008835</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>45803</v>
+        <v>45884</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5942,50 +5942,50 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>C-002104</t>
+          <t>C-004617</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CL-07061</t>
+          <t>CL-03029</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ET-02104</t>
+          <t>ET-04617</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P-016020</t>
+          <t>P-027615</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PR-01160</t>
+          <t>PR-01349</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BR-00160</t>
+          <t>BR-00204</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>E-004392</t>
+          <t>E-005629</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>45769</v>
+        <v>45839</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>

--- a/02.descargable/XLSX/01.XLSX correctos/devoluciones.xlsx
+++ b/02.descargable/XLSX/01.XLSX correctos/devoluciones.xlsx
@@ -497,50 +497,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C-001976</t>
+          <t>C-002220</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CL-02787</t>
+          <t>CL-01390</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ET-01976</t>
+          <t>ET-02220</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P-050733</t>
+          <t>P-011961</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PR-01420</t>
+          <t>PR-00140</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BR-00461</t>
+          <t>BR-00308</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-012237</t>
+          <t>E-008133</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45870</v>
+        <v>45761</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -552,41 +552,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C-003586</t>
+          <t>C-002084</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CL-00448</t>
+          <t>CL-09010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ET-03586</t>
+          <t>ET-02084</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P-028946</t>
+          <t>P-007253</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PR-00319</t>
+          <t>PR-00061</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BR-00065</t>
+          <t>BR-00160</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-001888</t>
+          <t>E-004441</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45844</v>
+        <v>45798</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -607,45 +607,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C-001757</t>
+          <t>C-001495</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CL-08551</t>
+          <t>CL-06867</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ET-01757</t>
+          <t>ET-01495</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P-039804</t>
+          <t>P-046086</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PR-00429</t>
+          <t>PR-01044</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BR-00360</t>
+          <t>BR-00091</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-009660</t>
+          <t>E-002651</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45875</v>
+        <v>45832</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -662,50 +662,50 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C-000897</t>
+          <t>C-002283</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CL-07210</t>
+          <t>CL-02907</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ET-00897</t>
+          <t>ET-02283</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P-044929</t>
+          <t>P-020727</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PR-00513</t>
+          <t>PR-00232</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BR-00057</t>
+          <t>BR-00174</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>E-001770</t>
+          <t>E-004738</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45783</v>
+        <v>45721</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -717,50 +717,50 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C-004344</t>
+          <t>C-000278</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CL-03354</t>
+          <t>CL-08191</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ET-04344</t>
+          <t>ET-00278</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P-045152</t>
+          <t>P-028064</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PR-01068</t>
+          <t>PR-00326</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BR-00410</t>
+          <t>BR-00349</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E-010820</t>
+          <t>E-009266</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45892</v>
+        <v>45897</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -772,50 +772,50 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C-003068</t>
+          <t>C-004978</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CL-07343</t>
+          <t>CL-00921</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ET-03068</t>
+          <t>ET-04978</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P-019869</t>
+          <t>P-015056</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PR-00197</t>
+          <t>PR-00186</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BR-00334</t>
+          <t>BR-00461</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E-008830</t>
+          <t>E-012129</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45734</v>
+        <v>45732</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -827,50 +827,50 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C-000734</t>
+          <t>C-004202</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CL-06119</t>
+          <t>CL-03771</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ET-00734</t>
+          <t>ET-04202</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P-003483</t>
+          <t>P-026269</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PR-01019</t>
+          <t>PR-01104</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BR-00029</t>
+          <t>BR-00236</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>E-000923</t>
+          <t>E-006351</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45739</v>
+        <v>45849</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -882,50 +882,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C-004892</t>
+          <t>C-000924</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CL-07868</t>
+          <t>CL-07326</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ET-04892</t>
+          <t>ET-00924</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P-031982</t>
+          <t>P-019593</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PR-00373</t>
+          <t>PR-01014</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BR-00289</t>
+          <t>BR-00427</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E-007772</t>
+          <t>E-011351</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45824</v>
+        <v>45742</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -937,45 +937,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C-000256</t>
+          <t>C-002838</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CL-09984</t>
+          <t>CL-00346</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ET-00256</t>
+          <t>ET-02838</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P-008938</t>
+          <t>P-011103</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PR-00109</t>
+          <t>PR-00127</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BR-00434</t>
+          <t>BR-00096</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E-011586</t>
+          <t>E-002731</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45837</v>
+        <v>45806</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -992,45 +992,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C-004941</t>
+          <t>C-004687</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CL-05015</t>
+          <t>CL-04545</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ET-04941</t>
+          <t>ET-04687</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P-018499</t>
+          <t>P-045463</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PR-00221</t>
+          <t>PR-00515</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BR-00231</t>
+          <t>BR-00415</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E-006220</t>
+          <t>E-010737</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45855</v>
+        <v>45794</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1047,50 +1047,50 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C-001397</t>
+          <t>C-002413</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CL-08907</t>
+          <t>CL-04173</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ET-01397</t>
+          <t>ET-02413</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P-009469</t>
+          <t>P-029052</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PR-01280</t>
+          <t>PR-00326</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BR-00273</t>
+          <t>BR-00055</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>E-007388</t>
+          <t>E-001703</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45733</v>
+        <v>45840</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1102,45 +1102,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C-003131</t>
+          <t>C-003518</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CL-02610</t>
+          <t>CL-02084</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ET-03131</t>
+          <t>ET-03518</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P-044826</t>
+          <t>P-027782</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PR-00783</t>
+          <t>PR-00837</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BR-00317</t>
+          <t>BR-00359</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>E-008580</t>
+          <t>E-009539</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45750</v>
+        <v>45770</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1157,45 +1157,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C-001862</t>
+          <t>C-001881</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CL-00422</t>
+          <t>CL-02226</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ET-01862</t>
+          <t>ET-01881</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P-044366</t>
+          <t>P-044755</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PR-00481</t>
+          <t>PR-01057</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BR-00229</t>
+          <t>BR-00366</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>E-006018</t>
+          <t>E-009660</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45839</v>
+        <v>45868</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1212,45 +1212,45 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C-004785</t>
+          <t>C-001677</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CL-00343</t>
+          <t>CL-00362</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ET-04785</t>
+          <t>ET-01677</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P-006124</t>
+          <t>P-017618</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PR-00890</t>
+          <t>PR-00999</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BR-00051</t>
+          <t>BR-00157</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>E-001660</t>
+          <t>E-004289</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45805</v>
+        <v>45835</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1267,45 +1267,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C-002512</t>
+          <t>C-001112</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CL-06995</t>
+          <t>CL-06672</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ET-02512</t>
+          <t>ET-01112</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P-050987</t>
+          <t>P-028226</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PR-01303</t>
+          <t>PR-01431</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BR-00463</t>
+          <t>BR-00025</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>E-012296</t>
+          <t>E-000875</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45724</v>
+        <v>45856</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1322,45 +1322,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C-004885</t>
+          <t>C-003999</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CL-04209</t>
+          <t>CL-02236</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ET-04885</t>
+          <t>ET-03999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P-053135</t>
+          <t>P-046116</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PR-00571</t>
+          <t>PR-00535</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BR-00167</t>
+          <t>BR-00343</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>E-004647</t>
+          <t>E-008793</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45773</v>
+        <v>45816</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1377,41 +1377,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C-000784</t>
+          <t>C-003158</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CL-02671</t>
+          <t>CL-06712</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ET-00784</t>
+          <t>ET-03158</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P-009555</t>
+          <t>P-027161</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PR-00132</t>
+          <t>PR-00650</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BR-00018</t>
+          <t>BR-00199</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>E-000771</t>
+          <t>E-005449</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45736</v>
+        <v>45833</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1432,50 +1432,50 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C-003124</t>
+          <t>C-004253</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CL-00092</t>
+          <t>CL-09628</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ET-03124</t>
+          <t>ET-04253</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P-014637</t>
+          <t>P-001154</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PR-00188</t>
+          <t>PR-00034</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BR-00129</t>
+          <t>BR-00138</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>E-003668</t>
+          <t>E-003803</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45789</v>
+        <v>45773</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1487,50 +1487,50 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C-000401</t>
+          <t>C-002446</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CL-03110</t>
+          <t>CL-09499</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ET-00401</t>
+          <t>ET-02446</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P-020615</t>
+          <t>P-023971</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PR-00223</t>
+          <t>PR-00242</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BR-00047</t>
+          <t>BR-00215</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>E-001547</t>
+          <t>E-005755</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45768</v>
+        <v>45818</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1542,45 +1542,45 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C-004963</t>
+          <t>C-002838</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CL-02982</t>
+          <t>CL-00346</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ET-04963</t>
+          <t>ET-02838</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P-030412</t>
+          <t>P-001483</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PR-00343</t>
+          <t>PR-00012</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BR-00386</t>
+          <t>BR-00096</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>E-010318</t>
+          <t>E-002731</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45826</v>
+        <v>45768</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1597,45 +1597,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C-002901</t>
+          <t>C-002690</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CL-03592</t>
+          <t>CL-01050</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ET-02901</t>
+          <t>ET-02690</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P-048571</t>
+          <t>P-002870</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PR-00528</t>
+          <t>PR-00008</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BR-00125</t>
+          <t>BR-00119</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>E-003601</t>
+          <t>E-003329</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45804</v>
+        <v>45826</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1652,50 +1652,50 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C-004072</t>
+          <t>C-001514</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CL-04191</t>
+          <t>CL-07730</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ET-04072</t>
+          <t>ET-01514</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P-010908</t>
+          <t>P-014382</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PR-00127</t>
+          <t>PR-00988</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BR-00025</t>
+          <t>BR-00126</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>E-000894</t>
+          <t>E-003595</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45870</v>
+        <v>45758</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1707,45 +1707,45 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C-002180</t>
+          <t>C-000368</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CL-07361</t>
+          <t>CL-07152</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ET-02180</t>
+          <t>ET-00368</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P-005533</t>
+          <t>P-043817</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PR-00062</t>
+          <t>PR-00476</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BR-00046</t>
+          <t>BR-00228</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>E-001518</t>
+          <t>E-005846</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45845</v>
+        <v>45879</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1762,50 +1762,50 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C-003243</t>
+          <t>C-000627</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CL-08041</t>
+          <t>CL-06357</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ET-03243</t>
+          <t>ET-00627</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P-023952</t>
+          <t>P-009044</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PR-00269</t>
+          <t>PR-00131</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BR-00215</t>
+          <t>BR-00080</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>E-005822</t>
+          <t>E-002255</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45879</v>
+        <v>45767</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1817,50 +1817,50 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C-000836</t>
+          <t>C-001550</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CL-01303</t>
+          <t>CL-08581</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ET-00836</t>
+          <t>ET-01550</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P-011548</t>
+          <t>P-023715</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PR-00101</t>
+          <t>PR-00278</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BR-00465</t>
+          <t>BR-00213</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>E-012384</t>
+          <t>E-005709</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45802</v>
+        <v>45793</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1872,50 +1872,50 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C-002313</t>
+          <t>C-004837</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CL-04293</t>
+          <t>CL-02877</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ET-02313</t>
+          <t>ET-04837</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P-020370</t>
+          <t>P-021492</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PR-00232</t>
+          <t>PR-00278</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BR-00184</t>
+          <t>BR-00194</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>E-004873</t>
+          <t>E-005226</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45755</v>
+        <v>45760</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1927,50 +1927,50 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C-000835</t>
+          <t>C-004579</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CL-02383</t>
+          <t>CL-03254</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ET-00835</t>
+          <t>ET-04579</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P-028206</t>
+          <t>P-019530</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PR-00288</t>
+          <t>PR-00222</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BR-00011</t>
+          <t>BR-00174</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>E-000634</t>
+          <t>E-004732</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45826</v>
+        <v>45795</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1982,50 +1982,50 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C-000047</t>
+          <t>C-000175</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CL-05928</t>
+          <t>CL-07015</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ET-00047</t>
+          <t>ET-00175</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P-026146</t>
+          <t>P-046100</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PR-00295</t>
+          <t>PR-00559</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BR-00273</t>
+          <t>BR-00019</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>E-007384</t>
+          <t>E-000773</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45801</v>
+        <v>45827</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2037,50 +2037,50 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C-000156</t>
+          <t>C-001571</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CL-08931</t>
+          <t>CL-04118</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ET-00156</t>
+          <t>ET-01571</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P-003347</t>
+          <t>P-036804</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PR-00009</t>
+          <t>PR-01190</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BR-00027</t>
+          <t>BR-00200</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>E-000913</t>
+          <t>E-005499</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45865</v>
+        <v>45840</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2092,50 +2092,50 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C-003933</t>
+          <t>C-003039</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CL-05862</t>
+          <t>CL-03595</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ET-03933</t>
+          <t>ET-03039</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P-049174</t>
+          <t>P-002517</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PR-00561</t>
+          <t>PR-01462</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BR-00448</t>
+          <t>BR-00104</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>E-011785</t>
+          <t>E-002845</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45713</v>
+        <v>45799</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2147,50 +2147,50 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C-001118</t>
+          <t>C-000237</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CL-05463</t>
+          <t>CL-03537</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ET-01118</t>
+          <t>ET-00237</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P-012725</t>
+          <t>P-009506</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PR-00919</t>
+          <t>PR-00877</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BR-00439</t>
+          <t>BR-00116</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>E-011675</t>
+          <t>E-003091</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45823</v>
+        <v>45813</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2202,45 +2202,45 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C-000170</t>
+          <t>C-002840</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CL-03882</t>
+          <t>CL-01856</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ET-00170</t>
+          <t>ET-02840</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P-027122</t>
+          <t>P-048523</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PR-00732</t>
+          <t>PR-00550</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BR-00041</t>
+          <t>BR-00039</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>E-001287</t>
+          <t>E-001099</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45854</v>
+        <v>45857</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2257,45 +2257,45 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C-001572</t>
+          <t>C-002957</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CL-07339</t>
+          <t>CL-05874</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ET-01572</t>
+          <t>ET-02957</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P-009820</t>
+          <t>P-050764</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PR-01493</t>
+          <t>PR-00604</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BR-00085</t>
+          <t>BR-00015</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>E-002547</t>
+          <t>E-000697</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45822</v>
+        <v>45840</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2312,45 +2312,45 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C-004499</t>
+          <t>C-000607</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CL-04221</t>
+          <t>CL-08227</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ET-04499</t>
+          <t>ET-00607</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P-052105</t>
+          <t>P-048515</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PR-00575</t>
+          <t>PR-01348</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BR-00215</t>
+          <t>BR-00440</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>E-005825</t>
+          <t>E-011605</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45793</v>
+        <v>45875</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2367,50 +2367,50 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C-000106</t>
+          <t>C-000005</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CL-09154</t>
+          <t>CL-06429</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ET-00106</t>
+          <t>ET-00005</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P-000962</t>
+          <t>P-003267</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PR-01078</t>
+          <t>PR-00009</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BR-00305</t>
+          <t>BR-00026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>E-007928</t>
+          <t>E-000883</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45794</v>
+        <v>45790</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2422,45 +2422,45 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C-004715</t>
+          <t>C-004178</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CL-01087</t>
+          <t>CL-01309</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ET-04715</t>
+          <t>ET-04178</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P-047007</t>
+          <t>P-004062</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PR-01134</t>
+          <t>PR-00782</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BR-00426</t>
+          <t>BR-00405</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>E-011365</t>
+          <t>E-010662</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45847</v>
+        <v>45862</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2477,50 +2477,50 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C-002085</t>
+          <t>C-000735</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CL-04442</t>
+          <t>CL-01400</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ET-02085</t>
+          <t>ET-00735</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P-026895</t>
+          <t>P-000610</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PR-00315</t>
+          <t>PR-00040</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>BR-00241</t>
+          <t>BR-00487</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>E-006613</t>
+          <t>E-012693</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45811</v>
+        <v>45893</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2532,45 +2532,45 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>C-001912</t>
+          <t>C-003626</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CL-02994</t>
+          <t>CL-09086</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ET-01912</t>
+          <t>ET-03626</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P-006109</t>
+          <t>P-005172</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PR-01478</t>
+          <t>PR-00081</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>BR-00051</t>
+          <t>BR-00382</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>E-001661</t>
+          <t>E-009908</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45796</v>
+        <v>45772</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2587,50 +2587,50 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C-003293</t>
+          <t>C-001017</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CL-04729</t>
+          <t>CL-08592</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ET-03293</t>
+          <t>ET-01017</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P-013850</t>
+          <t>P-003518</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PR-00154</t>
+          <t>PR-00044</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BR-00122</t>
+          <t>BR-00030</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>E-003461</t>
+          <t>E-000911</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45796</v>
+        <v>45875</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2642,50 +2642,50 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C-002505</t>
+          <t>C-002118</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CL-01145</t>
+          <t>CL-02315</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ET-02505</t>
+          <t>ET-02118</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P-036842</t>
+          <t>P-038665</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PR-00740</t>
+          <t>PR-00977</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>BR-00335</t>
+          <t>BR-00106</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>E-008835</t>
+          <t>E-002862</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45795</v>
+        <v>45865</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2697,50 +2697,50 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C-001640</t>
+          <t>C-004771</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CL-04100</t>
+          <t>CL-07063</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ET-01640</t>
+          <t>ET-04771</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P-031025</t>
+          <t>P-005448</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PR-00335</t>
+          <t>PR-00093</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>BR-00279</t>
+          <t>BR-00046</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>E-007597</t>
+          <t>E-001480</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45834</v>
+        <v>45784</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2752,50 +2752,50 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C-003505</t>
+          <t>C-000744</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CL-04253</t>
+          <t>CL-02717</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ET-03505</t>
+          <t>ET-00744</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P-016869</t>
+          <t>P-034534</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PR-01263</t>
+          <t>PR-00386</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BR-00223</t>
+          <t>BR-00312</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>E-005887</t>
+          <t>E-008331</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45884</v>
+        <v>45887</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2807,45 +2807,45 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C-003651</t>
+          <t>C-001527</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CL-03892</t>
+          <t>CL-01567</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ET-03651</t>
+          <t>ET-01527</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P-027490</t>
+          <t>P-052726</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PR-01015</t>
+          <t>PR-01012</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BR-00230</t>
+          <t>BR-00479</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>E-006131</t>
+          <t>E-012600</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45711</v>
+        <v>45743</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2862,45 +2862,45 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C-000780</t>
+          <t>C-004331</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CL-09305</t>
+          <t>CL-03443</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ET-00780</t>
+          <t>ET-04331</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P-012247</t>
+          <t>P-046268</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PR-01479</t>
+          <t>PR-01121</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BR-00329</t>
+          <t>BR-00421</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>E-008781</t>
+          <t>E-011086</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45732</v>
+        <v>45865</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2917,50 +2917,50 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C-004300</t>
+          <t>C-002264</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CL-06032</t>
+          <t>CL-07298</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ET-04300</t>
+          <t>ET-02264</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P-050926</t>
+          <t>P-053760</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PR-00606</t>
+          <t>PR-00608</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BR-00462</t>
+          <t>BR-00492</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>E-012286</t>
+          <t>E-012722</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45723</v>
+        <v>45762</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2972,50 +2972,50 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C-002082</t>
+          <t>C-000855</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CL-01608</t>
+          <t>CL-06021</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ET-02082</t>
+          <t>ET-00855</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P-030279</t>
+          <t>P-009161</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PR-00929</t>
+          <t>PR-00140</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BR-00419</t>
+          <t>BR-00259</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>E-010922</t>
+          <t>E-006787</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45783</v>
+        <v>45821</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3027,50 +3027,50 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C-000245</t>
+          <t>C-003229</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CL-07335</t>
+          <t>CL-00032</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ET-00245</t>
+          <t>ET-03229</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P-010844</t>
+          <t>P-021680</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PR-00963</t>
+          <t>PR-00271</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>BR-00094</t>
+          <t>BR-00003</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>E-002738</t>
+          <t>E-000294</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45746</v>
+        <v>45843</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3082,50 +3082,50 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C-001118</t>
+          <t>C-002732</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CL-05463</t>
+          <t>CL-05084</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ET-01118</t>
+          <t>ET-02732</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P-018748</t>
+          <t>P-037799</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PR-00983</t>
+          <t>PR-01204</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BR-00439</t>
+          <t>BR-00344</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>E-011675</t>
+          <t>E-008958</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45883</v>
+        <v>45840</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3137,45 +3137,45 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C-003095</t>
+          <t>C-000234</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CL-02551</t>
+          <t>CL-06620</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ET-03095</t>
+          <t>ET-00234</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P-007017</t>
+          <t>P-010966</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PR-01181</t>
+          <t>PR-01286</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>BR-00060</t>
+          <t>BR-00042</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>E-001813</t>
+          <t>E-001295</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45821</v>
+        <v>45829</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3192,45 +3192,45 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C-003581</t>
+          <t>C-004613</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CL-06417</t>
+          <t>CL-01977</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ET-03581</t>
+          <t>ET-04613</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P-019445</t>
+          <t>P-005331</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PR-01136</t>
+          <t>PR-00799</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>BR-00173</t>
+          <t>BR-00393</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>E-004757</t>
+          <t>E-010450</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45798</v>
+        <v>45878</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3247,50 +3247,50 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C-000475</t>
+          <t>C-003618</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CL-00966</t>
+          <t>CL-04346</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ET-00475</t>
+          <t>ET-03618</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P-027939</t>
+          <t>P-009112</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PR-00294</t>
+          <t>PR-00135</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BR-00251</t>
+          <t>BR-00119</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>E-006775</t>
+          <t>E-003332</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45820</v>
+        <v>45721</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -3302,41 +3302,41 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C-001178</t>
+          <t>C-003056</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CL-06113</t>
+          <t>CL-07675</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ET-01178</t>
+          <t>ET-03056</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P-041252</t>
+          <t>P-024948</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PR-00840</t>
+          <t>PR-00269</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>BR-00377</t>
+          <t>BR-00291</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>E-009855</t>
+          <t>E-007719</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45849</v>
+        <v>45748</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3357,50 +3357,50 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C-002508</t>
+          <t>C-003601</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CL-06057</t>
+          <t>CL-05671</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ET-02508</t>
+          <t>ET-03601</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P-022627</t>
+          <t>P-027983</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PR-01039</t>
+          <t>PR-01087</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>BR-00343</t>
+          <t>BR-00098</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>E-008891</t>
+          <t>E-002777</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45732</v>
+        <v>45851</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3412,50 +3412,50 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C-001480</t>
+          <t>C-004614</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CL-08062</t>
+          <t>CL-08956</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ET-01480</t>
+          <t>ET-04614</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P-006101</t>
+          <t>P-046490</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PR-00081</t>
+          <t>PR-00534</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>BR-00019</t>
+          <t>BR-00318</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>E-000795</t>
+          <t>E-008506</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45768</v>
+        <v>45878</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3467,45 +3467,45 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C-001106</t>
+          <t>C-003679</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CL-04970</t>
+          <t>CL-03137</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ET-01106</t>
+          <t>ET-03679</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P-029598</t>
+          <t>P-000373</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PR-01190</t>
+          <t>PR-00760</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>BR-00269</t>
+          <t>BR-00002</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>E-007203</t>
+          <t>E-000154</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45855</v>
+        <v>45729</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3522,45 +3522,45 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C-000700</t>
+          <t>C-003364</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CL-06106</t>
+          <t>CL-05676</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ET-00700</t>
+          <t>ET-03364</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P-030709</t>
+          <t>P-033423</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PR-00340</t>
+          <t>PR-00899</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>BR-00213</t>
+          <t>BR-00305</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>E-005797</t>
+          <t>E-007882</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45748</v>
+        <v>45881</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3577,45 +3577,45 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C-002079</t>
+          <t>C-002972</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CL-05060</t>
+          <t>CL-00551</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ET-02079</t>
+          <t>ET-02972</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P-047026</t>
+          <t>P-009162</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PR-00525</t>
+          <t>PR-00140</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>BR-00128</t>
+          <t>BR-00081</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>E-003659</t>
+          <t>E-002317</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45888</v>
+        <v>45752</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3632,50 +3632,50 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C-002330</t>
+          <t>C-003903</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CL-05187</t>
+          <t>CL-08594</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ET-02330</t>
+          <t>ET-03903</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P-003629</t>
+          <t>P-011610</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PR-01019</t>
+          <t>PR-00141</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BR-00031</t>
+          <t>BR-00087</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>E-000937</t>
+          <t>E-002571</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45758</v>
+        <v>45739</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -3687,45 +3687,45 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C-004928</t>
+          <t>C-002968</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CL-05381</t>
+          <t>CL-01679</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ET-04928</t>
+          <t>ET-02968</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P-012277</t>
+          <t>P-052446</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PR-00127</t>
+          <t>PR-00570</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>BR-00458</t>
+          <t>BR-00275</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>E-012106</t>
+          <t>E-007378</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45718</v>
+        <v>45852</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3742,50 +3742,50 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C-002313</t>
+          <t>C-004674</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CL-04293</t>
+          <t>CL-04042</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ET-02313</t>
+          <t>ET-04674</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P-019690</t>
+          <t>P-031790</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PR-01298</t>
+          <t>PR-00374</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BR-00184</t>
+          <t>BR-00287</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>E-004873</t>
+          <t>E-007653</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45884</v>
+        <v>45745</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -3797,45 +3797,45 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C-004958</t>
+          <t>C-004678</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CL-02808</t>
+          <t>CL-06524</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ET-04958</t>
+          <t>ET-04678</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P-037790</t>
+          <t>P-018134</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PR-01223</t>
+          <t>PR-00197</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BR-00052</t>
+          <t>BR-00095</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>E-001677</t>
+          <t>E-002713</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45800</v>
+        <v>45851</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3852,50 +3852,50 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C-000963</t>
+          <t>C-003306</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CL-02726</t>
+          <t>CL-08782</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ET-00963</t>
+          <t>ET-03306</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P-046996</t>
+          <t>P-052458</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PR-00551</t>
+          <t>PR-01033</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BR-00426</t>
+          <t>BR-00350</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>E-011397</t>
+          <t>E-009320</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45835</v>
+        <v>45812</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3907,50 +3907,50 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C-001317</t>
+          <t>C-002377</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CL-01665</t>
+          <t>CL-03495</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ET-01317</t>
+          <t>ET-02377</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P-023208</t>
+          <t>P-011187</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PR-00247</t>
+          <t>PR-00137</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>BR-00207</t>
+          <t>BR-00122</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>E-005688</t>
+          <t>E-003471</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45772</v>
+        <v>45716</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3962,41 +3962,41 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C-000862</t>
+          <t>C-001897</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CL-05228</t>
+          <t>CL-01589</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ET-00862</t>
+          <t>ET-01897</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P-007412</t>
+          <t>P-042499</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PR-00083</t>
+          <t>PR-00504</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>BR-00082</t>
+          <t>BR-00386</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>E-002411</t>
+          <t>E-010220</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45867</v>
+        <v>45716</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -4017,50 +4017,50 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C-002313</t>
+          <t>C-002246</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CL-04293</t>
+          <t>CL-02914</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ET-02313</t>
+          <t>ET-02246</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P-020370</t>
+          <t>P-017128</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PR-00232</t>
+          <t>PR-00211</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BR-00184</t>
+          <t>BR-00154</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>E-004873</t>
+          <t>E-004118</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45794</v>
+        <v>45804</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4072,50 +4072,50 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C-002645</t>
+          <t>C-004882</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CL-01529</t>
+          <t>CL-01033</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ET-02645</t>
+          <t>ET-04882</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P-010164</t>
+          <t>P-022180</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PR-00141</t>
+          <t>PR-00246</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>BR-00088</t>
+          <t>BR-00247</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>E-002635</t>
+          <t>E-006632</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45801</v>
+        <v>45818</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4127,45 +4127,45 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C-003339</t>
+          <t>C-003408</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CL-05229</t>
+          <t>CL-02660</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ET-03339</t>
+          <t>ET-03408</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P-034583</t>
+          <t>P-046998</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PR-01385</t>
+          <t>PR-00552</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BR-00312</t>
+          <t>BR-00426</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>E-008408</t>
+          <t>E-011304</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45840</v>
+        <v>45723</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4182,45 +4182,45 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C-004722</t>
+          <t>C-001272</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CL-04621</t>
+          <t>CL-09838</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ET-04722</t>
+          <t>ET-01272</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P-013081</t>
+          <t>P-038123</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PR-00828</t>
+          <t>PR-00465</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BR-00117</t>
+          <t>BR-00346</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>E-003260</t>
+          <t>E-009110</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45731</v>
+        <v>45723</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4237,45 +4237,45 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C-001433</t>
+          <t>C-001046</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CL-09698</t>
+          <t>CL-08784</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ET-01433</t>
+          <t>ET-01046</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P-023702</t>
+          <t>P-015489</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PR-00994</t>
+          <t>PR-00178</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BR-00212</t>
+          <t>BR-00137</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>E-005771</t>
+          <t>E-003784</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45727</v>
+        <v>45715</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4292,45 +4292,45 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>C-004000</t>
+          <t>C-004149</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CL-05187</t>
+          <t>CL-05070</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ET-04000</t>
+          <t>ET-04149</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P-019398</t>
+          <t>P-031634</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PR-00232</t>
+          <t>PR-00775</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BR-00314</t>
+          <t>BR-00360</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>E-008539</t>
+          <t>E-009553</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45793</v>
+        <v>45796</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4347,50 +4347,50 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C-000199</t>
+          <t>C-002076</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CL-02266</t>
+          <t>CL-07652</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ET-00199</t>
+          <t>ET-02076</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P-024747</t>
+          <t>P-014327</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PR-01254</t>
+          <t>PR-00186</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>BR-00225</t>
+          <t>BR-00464</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>E-005901</t>
+          <t>E-012277</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45887</v>
+        <v>45830</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C-000269</t>
+          <t>C-003158</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CL-02691</t>
+          <t>CL-06712</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ET-00269</t>
+          <t>ET-03158</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P-027181</t>
+          <t>P-014867</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PR-00898</t>
+          <t>PR-00824</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>BR-00244</t>
+          <t>BR-00199</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>E-006656</t>
+          <t>E-005449</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45772</v>
+        <v>45881</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4457,50 +4457,50 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C-001016</t>
+          <t>C-004506</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CL-07493</t>
+          <t>CL-03106</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ET-01016</t>
+          <t>ET-04506</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P-027873</t>
+          <t>P-004751</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PR-01015</t>
+          <t>PR-00055</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>BR-00273</t>
+          <t>BR-00041</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>E-007401</t>
+          <t>E-001273</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45769</v>
+        <v>45839</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4512,50 +4512,50 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C-003311</t>
+          <t>C-002824</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CL-09873</t>
+          <t>CL-07038</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ET-03311</t>
+          <t>ET-02824</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P-029336</t>
+          <t>P-051727</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PR-00357</t>
+          <t>PR-01353</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>BR-00180</t>
+          <t>BR-00468</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>E-004846</t>
+          <t>E-012421</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45795</v>
+        <v>45884</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -4567,45 +4567,45 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C-003897</t>
+          <t>C-000792</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CL-05317</t>
+          <t>CL-00106</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ET-03897</t>
+          <t>ET-00792</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P-003552</t>
+          <t>P-050285</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PR-00035</t>
+          <t>PR-00801</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BR-00030</t>
+          <t>BR-00458</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>E-000928</t>
+          <t>E-011948</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45726</v>
+        <v>45852</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4622,50 +4622,50 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C-001344</t>
+          <t>C-003463</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CL-07678</t>
+          <t>CL-04517</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ET-01344</t>
+          <t>ET-03463</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P-047631</t>
+          <t>P-039628</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PR-00563</t>
+          <t>PR-00434</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>BR-00431</t>
+          <t>BR-00251</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>E-011537</t>
+          <t>E-006701</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45887</v>
+        <v>45730</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -4677,41 +4677,41 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C-001911</t>
+          <t>C-000278</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CL-09163</t>
+          <t>CL-08191</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ET-01911</t>
+          <t>ET-00278</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P-028145</t>
+          <t>P-024117</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PR-01120</t>
+          <t>PR-00270</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>BR-00231</t>
+          <t>BR-00349</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>E-006211</t>
+          <t>E-009266</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45765</v>
+        <v>45822</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4732,50 +4732,50 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C-004665</t>
+          <t>C-004203</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CL-06162</t>
+          <t>CL-03762</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ET-04665</t>
+          <t>ET-04203</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P-050485</t>
+          <t>P-043587</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PR-00583</t>
+          <t>PR-01246</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>BR-00459</t>
+          <t>BR-00394</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>E-012162</t>
+          <t>E-010480</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45775</v>
+        <v>45797</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4787,50 +4787,50 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C-000586</t>
+          <t>C-004977</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CL-01412</t>
+          <t>CL-03169</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ET-00586</t>
+          <t>ET-04977</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P-049497</t>
+          <t>P-016427</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PR-00550</t>
+          <t>PR-00186</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BR-00452</t>
+          <t>BR-00170</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>E-011816</t>
+          <t>E-004674</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45863</v>
+        <v>45769</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -4842,50 +4842,50 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C-002019</t>
+          <t>C-000078</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CL-09953</t>
+          <t>CL-03328</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ET-02019</t>
+          <t>ET-00078</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P-033062</t>
+          <t>P-041748</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PR-00982</t>
+          <t>PR-01355</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BR-00373</t>
+          <t>BR-00281</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>E-009828</t>
+          <t>E-007543</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45825</v>
+        <v>45752</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4897,50 +4897,50 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>C-002957</t>
+          <t>C-002885</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CL-01457</t>
+          <t>CL-06468</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ET-02957</t>
+          <t>ET-02885</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P-033846</t>
+          <t>P-049132</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PR-00395</t>
+          <t>PR-00732</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>BR-00196</t>
+          <t>BR-00199</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>E-005328</t>
+          <t>E-005426</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45824</v>
+        <v>45875</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4952,41 +4952,41 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>C-002758</t>
+          <t>C-004344</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CL-02225</t>
+          <t>CL-07427</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ET-02758</t>
+          <t>ET-04344</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P-009674</t>
+          <t>P-028101</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PR-00623</t>
+          <t>PR-00689</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>BR-00084</t>
+          <t>BR-00253</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>E-002497</t>
+          <t>E-006739</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45889</v>
+        <v>45858</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -5007,50 +5007,50 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>C-004205</t>
+          <t>C-001132</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CL-01490</t>
+          <t>CL-05612</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ET-04205</t>
+          <t>ET-01132</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P-035948</t>
+          <t>P-037100</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PR-00886</t>
+          <t>PR-00420</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BR-00325</t>
+          <t>BR-00006</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>E-008728</t>
+          <t>E-000455</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45787</v>
+        <v>45849</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -5062,45 +5062,45 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C-001412</t>
+          <t>C-004235</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CL-09310</t>
+          <t>CL-09557</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ET-01412</t>
+          <t>ET-04235</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P-046946</t>
+          <t>P-010604</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PR-00638</t>
+          <t>PR-01345</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>BR-00425</t>
+          <t>BR-00276</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>E-011343</t>
+          <t>E-007458</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45719</v>
+        <v>45761</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5117,45 +5117,45 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C-002603</t>
+          <t>C-003277</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CL-07598</t>
+          <t>CL-01508</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ET-02603</t>
+          <t>ET-03277</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P-049197</t>
+          <t>P-027329</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PR-00550</t>
+          <t>PR-00319</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>BR-00364</t>
+          <t>BR-00328</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>E-009730</t>
+          <t>E-008679</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45722</v>
+        <v>45868</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5172,45 +5172,45 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>C-002834</t>
+          <t>C-004705</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CL-05737</t>
+          <t>CL-00819</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ET-02834</t>
+          <t>ET-04705</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P-016290</t>
+          <t>P-048272</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PR-00188</t>
+          <t>PR-00528</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BR-00274</t>
+          <t>BR-00437</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>E-007452</t>
+          <t>E-011547</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45822</v>
+        <v>45859</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5227,50 +5227,50 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C-002328</t>
+          <t>C-001830</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CL-05168</t>
+          <t>CL-08444</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ET-02328</t>
+          <t>ET-01830</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P-005652</t>
+          <t>P-053898</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PR-01181</t>
+          <t>PR-00987</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>BR-00190</t>
+          <t>BR-00235</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>E-004912</t>
+          <t>E-006334</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45756</v>
+        <v>45730</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -5282,50 +5282,50 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>C-004955</t>
+          <t>C-002470</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CL-02521</t>
+          <t>CL-04802</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ET-04955</t>
+          <t>ET-02470</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P-027379</t>
+          <t>P-021803</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PR-01120</t>
+          <t>PR-01196</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>BR-00245</t>
+          <t>BR-00454</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>E-006686</t>
+          <t>E-011735</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45804</v>
+        <v>45778</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5337,50 +5337,50 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C-004075</t>
+          <t>C-001652</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CL-05113</t>
+          <t>CL-09032</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ET-04075</t>
+          <t>ET-01652</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P-045694</t>
+          <t>P-022659</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PR-00504</t>
+          <t>PR-00279</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BR-00194</t>
+          <t>BR-00202</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>E-005263</t>
+          <t>E-005522</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45746</v>
+        <v>45759</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5392,45 +5392,45 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>C-001178</t>
+          <t>C-002064</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CL-06113</t>
+          <t>CL-07474</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ET-01178</t>
+          <t>ET-02064</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P-041252</t>
+          <t>P-006442</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PR-00840</t>
+          <t>PR-00059</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>BR-00377</t>
+          <t>BR-00094</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>E-009855</t>
+          <t>E-002703</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>45712</v>
+        <v>45872</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5447,50 +5447,50 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C-003726</t>
+          <t>C-000971</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CL-01746</t>
+          <t>CL-02536</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ET-03726</t>
+          <t>ET-00971</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P-033410</t>
+          <t>P-022376</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PR-00381</t>
+          <t>PR-00276</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>BR-00353</t>
+          <t>BR-00271</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>E-009539</t>
+          <t>E-007230</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45740</v>
+        <v>45803</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -5502,50 +5502,50 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C-004082</t>
+          <t>C-000261</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CL-05876</t>
+          <t>CL-07468</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ET-04082</t>
+          <t>ET-00261</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P-018261</t>
+          <t>P-022454</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PR-01433</t>
+          <t>PR-00272</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>BR-00361</t>
+          <t>BR-00200</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>E-009674</t>
+          <t>E-005491</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>45884</v>
+        <v>45829</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -5557,50 +5557,50 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>C-001448</t>
+          <t>C-002449</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CL-05632</t>
+          <t>CL-02843</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ET-01448</t>
+          <t>ET-02449</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P-014382</t>
+          <t>P-047421</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PR-00151</t>
+          <t>PR-00562</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>BR-00126</t>
+          <t>BR-00345</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>E-003614</t>
+          <t>E-009079</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45741</v>
+        <v>45874</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5612,50 +5612,50 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C-003259</t>
+          <t>C-002484</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CL-05832</t>
+          <t>CL-03620</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ET-03259</t>
+          <t>ET-02484</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P-031758</t>
+          <t>P-021291</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PR-00993</t>
+          <t>PR-01277</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BR-00194</t>
+          <t>BR-00068</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>E-005245</t>
+          <t>E-001874</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>45760</v>
+        <v>45869</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -5667,50 +5667,50 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C-002389</t>
+          <t>C-004684</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CL-07112</t>
+          <t>CL-08829</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ET-02389</t>
+          <t>ET-04684</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P-012428</t>
+          <t>P-041320</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PR-01280</t>
+          <t>PR-01257</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BR-00472</t>
+          <t>BR-00378</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>E-012564</t>
+          <t>E-009759</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>45806</v>
+        <v>45768</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -5722,45 +5722,45 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>C-001607</t>
+          <t>C-002120</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CL-00270</t>
+          <t>CL-04570</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ET-01607</t>
+          <t>ET-02120</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P-050245</t>
+          <t>P-002496</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PR-00984</t>
+          <t>PR-00782</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>BR-00458</t>
+          <t>BR-00277</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>E-012017</t>
+          <t>E-007479</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>45823</v>
+        <v>45831</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5777,45 +5777,45 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>C-004162</t>
+          <t>C-003056</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CL-07648</t>
+          <t>CL-07675</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ET-04162</t>
+          <t>ET-03056</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P-039301</t>
+          <t>P-032202</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PR-00457</t>
+          <t>PR-00364</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>BR-00183</t>
+          <t>BR-00291</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>E-004867</t>
+          <t>E-007719</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45793</v>
+        <v>45719</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5832,50 +5832,50 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C-000562</t>
+          <t>C-003812</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CL-04544</t>
+          <t>CL-08437</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ET-00562</t>
+          <t>ET-03812</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P-045846</t>
+          <t>P-021686</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PR-00741</t>
+          <t>PR-00241</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BR-00419</t>
+          <t>BR-00374</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>E-010910</t>
+          <t>E-009732</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>45809</v>
+        <v>45878</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -5887,50 +5887,50 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>C-002505</t>
+          <t>C-002413</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CL-01145</t>
+          <t>CL-04173</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ET-02505</t>
+          <t>ET-02413</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P-036842</t>
+          <t>P-002801</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PR-00740</t>
+          <t>PR-00782</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>BR-00335</t>
+          <t>BR-00055</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>E-008835</t>
+          <t>E-001703</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>45884</v>
+        <v>45772</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5942,50 +5942,50 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>C-004617</t>
+          <t>C-002392</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CL-03029</t>
+          <t>CL-06916</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ET-04617</t>
+          <t>ET-02392</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P-027615</t>
+          <t>P-007654</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PR-01349</t>
+          <t>PR-00864</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BR-00204</t>
+          <t>BR-00344</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>E-005629</t>
+          <t>E-008976</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>45839</v>
+        <v>45886</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>

--- a/02.descargable/XLSX/01.XLSX correctos/devoluciones.xlsx
+++ b/02.descargable/XLSX/01.XLSX correctos/devoluciones.xlsx
@@ -497,45 +497,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C-002220</t>
+          <t>C-003767</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CL-01390</t>
+          <t>CL-05776</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ET-02220</t>
+          <t>ET-03767</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P-011961</t>
+          <t>P-001492</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PR-00140</t>
+          <t>PR-00968</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BR-00308</t>
+          <t>BR-00009</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-008133</t>
+          <t>E-000553</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45761</v>
+        <v>45874</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -552,50 +552,50 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C-002084</t>
+          <t>C-000248</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CL-09010</t>
+          <t>CL-00116</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ET-02084</t>
+          <t>ET-00248</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P-007253</t>
+          <t>P-032801</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PR-00061</t>
+          <t>PR-01201</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BR-00160</t>
+          <t>BR-00356</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-004441</t>
+          <t>E-009559</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45798</v>
+        <v>45806</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -607,45 +607,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C-001495</t>
+          <t>C-004629</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CL-06867</t>
+          <t>CL-02317</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ET-01495</t>
+          <t>ET-04629</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P-046086</t>
+          <t>P-044932</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PR-01044</t>
+          <t>PR-00514</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BR-00091</t>
+          <t>BR-00408</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-002651</t>
+          <t>E-010741</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45832</v>
+        <v>45864</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -662,50 +662,50 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C-002283</t>
+          <t>C-003403</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CL-02907</t>
+          <t>CL-08882</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ET-02283</t>
+          <t>ET-03403</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P-020727</t>
+          <t>P-034992</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PR-00232</t>
+          <t>PR-00385</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BR-00174</t>
+          <t>BR-00315</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>E-004738</t>
+          <t>E-008522</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45721</v>
+        <v>45765</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -717,50 +717,50 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C-000278</t>
+          <t>C-004409</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CL-08191</t>
+          <t>CL-09499</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ET-00278</t>
+          <t>ET-04409</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P-028064</t>
+          <t>P-044609</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PR-00326</t>
+          <t>PR-00503</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BR-00349</t>
+          <t>BR-00262</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E-009266</t>
+          <t>E-006862</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45897</v>
+        <v>45879</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -772,50 +772,50 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C-004978</t>
+          <t>C-000643</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CL-00921</t>
+          <t>CL-05966</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ET-04978</t>
+          <t>ET-00643</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P-015056</t>
+          <t>P-003735</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PR-00186</t>
+          <t>PR-01156</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BR-00461</t>
+          <t>BR-00249</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E-012129</t>
+          <t>E-006739</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45732</v>
+        <v>45733</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -827,45 +827,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C-004202</t>
+          <t>C-001495</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CL-03771</t>
+          <t>CL-00283</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ET-04202</t>
+          <t>ET-01495</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P-026269</t>
+          <t>P-032953</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PR-01104</t>
+          <t>PR-00375</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BR-00236</t>
+          <t>BR-00301</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>E-006351</t>
+          <t>E-007843</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45849</v>
+        <v>45749</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -882,50 +882,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C-000924</t>
+          <t>C-004121</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CL-07326</t>
+          <t>CL-09602</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ET-00924</t>
+          <t>ET-04121</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P-019593</t>
+          <t>P-022125</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PR-01014</t>
+          <t>PR-00960</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BR-00427</t>
+          <t>BR-00198</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E-011351</t>
+          <t>E-005410</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45742</v>
+        <v>45822</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -937,50 +937,50 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C-002838</t>
+          <t>C-000458</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CL-00346</t>
+          <t>CL-06351</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ET-02838</t>
+          <t>ET-00458</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P-011103</t>
+          <t>P-016431</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PR-00127</t>
+          <t>PR-00187</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BR-00096</t>
+          <t>BR-00352</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E-002731</t>
+          <t>E-009470</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45806</v>
+        <v>45802</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -992,50 +992,50 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C-004687</t>
+          <t>C-001658</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CL-04545</t>
+          <t>CL-06585</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ET-04687</t>
+          <t>ET-01658</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P-045463</t>
+          <t>P-039087</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PR-00515</t>
+          <t>PR-00469</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BR-00415</t>
+          <t>BR-00198</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E-010737</t>
+          <t>E-005413</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45794</v>
+        <v>45885</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1047,50 +1047,50 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C-002413</t>
+          <t>C-004036</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CL-04173</t>
+          <t>CL-08165</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ET-02413</t>
+          <t>ET-04036</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P-029052</t>
+          <t>P-049526</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PR-00326</t>
+          <t>PR-00523</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BR-00055</t>
+          <t>BR-00452</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>E-001703</t>
+          <t>E-011770</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45840</v>
+        <v>45799</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1102,50 +1102,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C-003518</t>
+          <t>C-002435</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CL-02084</t>
+          <t>CL-04390</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ET-03518</t>
+          <t>ET-02435</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P-027782</t>
+          <t>P-047558</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PR-00837</t>
+          <t>PR-00523</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BR-00359</t>
+          <t>BR-00161</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>E-009539</t>
+          <t>E-004486</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45770</v>
+        <v>45744</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1157,41 +1157,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C-001881</t>
+          <t>C-001156</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CL-02226</t>
+          <t>CL-07909</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ET-01881</t>
+          <t>ET-01156</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P-044755</t>
+          <t>P-017630</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PR-01057</t>
+          <t>PR-00859</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BR-00366</t>
+          <t>BR-00466</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>E-009660</t>
+          <t>E-012394</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45868</v>
+        <v>45816</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1212,45 +1212,45 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C-001677</t>
+          <t>C-000315</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CL-00362</t>
+          <t>CL-08716</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ET-01677</t>
+          <t>ET-00315</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P-017618</t>
+          <t>P-049546</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PR-00999</t>
+          <t>PR-00560</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BR-00157</t>
+          <t>BR-00453</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>E-004289</t>
+          <t>E-011776</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45835</v>
+        <v>45848</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1267,50 +1267,50 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C-001112</t>
+          <t>C-000226</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CL-06672</t>
+          <t>CL-08571</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ET-01112</t>
+          <t>ET-00226</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P-028226</t>
+          <t>P-040241</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PR-01431</t>
+          <t>PR-01188</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BR-00025</t>
+          <t>BR-00322</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>E-000875</t>
+          <t>E-008643</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45856</v>
+        <v>45777</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1322,41 +1322,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C-003999</t>
+          <t>C-004578</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CL-02236</t>
+          <t>CL-05994</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ET-03999</t>
+          <t>ET-04578</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P-046116</t>
+          <t>P-024349</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PR-00535</t>
+          <t>PR-01055</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BR-00343</t>
+          <t>BR-00220</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>E-008793</t>
+          <t>E-005846</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45816</v>
+        <v>45859</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1377,50 +1377,50 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C-003158</t>
+          <t>C-000142</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CL-06712</t>
+          <t>CL-07609</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ET-03158</t>
+          <t>ET-00142</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P-027161</t>
+          <t>P-014370</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PR-00650</t>
+          <t>PR-01281</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BR-00199</t>
+          <t>BR-00233</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>E-005449</t>
+          <t>E-006295</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45833</v>
+        <v>45828</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1432,50 +1432,50 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C-004253</t>
+          <t>C-002851</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CL-09628</t>
+          <t>CL-02576</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ET-04253</t>
+          <t>ET-02851</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P-001154</t>
+          <t>P-033424</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PR-00034</t>
+          <t>PR-00400</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BR-00138</t>
+          <t>BR-00305</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>E-003803</t>
+          <t>E-007965</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45773</v>
+        <v>45804</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -1487,22 +1487,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C-002446</t>
+          <t>C-002785</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CL-09499</t>
+          <t>CL-06941</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ET-02446</t>
+          <t>ET-02785</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P-023971</t>
+          <t>P-024737</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1512,20 +1512,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BR-00215</t>
+          <t>BR-00225</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>E-005755</t>
+          <t>E-005873</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45818</v>
+        <v>45730</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1542,41 +1542,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C-002838</t>
+          <t>C-004327</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CL-00346</t>
+          <t>CL-03872</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ET-02838</t>
+          <t>ET-04327</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P-001483</t>
+          <t>P-010082</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PR-00012</t>
+          <t>PR-00131</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BR-00096</t>
+          <t>BR-00087</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>E-002731</t>
+          <t>E-002596</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45768</v>
+        <v>45884</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -1597,45 +1597,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C-002690</t>
+          <t>C-002678</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CL-01050</t>
+          <t>CL-02268</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ET-02690</t>
+          <t>ET-02678</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P-002870</t>
+          <t>P-004038</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PR-00008</t>
+          <t>PR-00006</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BR-00119</t>
+          <t>BR-00120</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>E-003329</t>
+          <t>E-003391</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45826</v>
+        <v>45858</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1652,45 +1652,45 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C-001514</t>
+          <t>C-002246</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CL-07730</t>
+          <t>CL-00803</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ET-01514</t>
+          <t>ET-02246</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P-014382</t>
+          <t>P-001772</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PR-00988</t>
+          <t>PR-00943</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BR-00126</t>
+          <t>BR-00155</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>E-003595</t>
+          <t>E-004222</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45758</v>
+        <v>45875</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1707,45 +1707,45 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C-000368</t>
+          <t>C-003339</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CL-07152</t>
+          <t>CL-00359</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ET-00368</t>
+          <t>ET-03339</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P-043817</t>
+          <t>P-015460</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PR-00476</t>
+          <t>PR-00187</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BR-00228</t>
+          <t>BR-00370</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>E-005846</t>
+          <t>E-009761</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45879</v>
+        <v>45875</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1762,50 +1762,50 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C-000627</t>
+          <t>C-001646</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CL-06357</t>
+          <t>CL-02411</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ET-00627</t>
+          <t>ET-01646</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P-009044</t>
+          <t>P-047964</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PR-00131</t>
+          <t>PR-01298</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BR-00080</t>
+          <t>BR-00434</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>E-002255</t>
+          <t>E-011554</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45767</v>
+        <v>45884</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1817,37 +1817,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C-001550</t>
+          <t>C-001412</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CL-08581</t>
+          <t>CL-04652</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ET-01550</t>
+          <t>ET-01412</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P-023715</t>
+          <t>P-045915</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PR-00278</t>
+          <t>PR-01134</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BR-00213</t>
+          <t>BR-00419</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>E-005709</t>
+          <t>E-010912</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1872,45 +1872,45 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C-004837</t>
+          <t>C-001286</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CL-02877</t>
+          <t>CL-03022</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ET-04837</t>
+          <t>ET-01286</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P-021492</t>
+          <t>P-047670</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PR-00278</t>
+          <t>PR-00525</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BR-00194</t>
+          <t>BR-00078</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>E-005226</t>
+          <t>E-002217</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45760</v>
+        <v>45889</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1927,50 +1927,50 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C-004579</t>
+          <t>C-000953</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CL-03254</t>
+          <t>CL-00990</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ET-04579</t>
+          <t>ET-00953</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P-019530</t>
+          <t>P-048385</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PR-00222</t>
+          <t>PR-00531</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BR-00174</t>
+          <t>BR-00384</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>E-004732</t>
+          <t>E-010144</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45795</v>
+        <v>45739</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -1982,50 +1982,50 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C-000175</t>
+          <t>C-004613</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CL-07015</t>
+          <t>CL-08190</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ET-00175</t>
+          <t>ET-04613</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P-046100</t>
+          <t>P-029198</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PR-00559</t>
+          <t>PR-01376</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BR-00019</t>
+          <t>BR-00267</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>E-000773</t>
+          <t>E-006888</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45827</v>
+        <v>45803</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2037,50 +2037,50 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C-001571</t>
+          <t>C-000032</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CL-04118</t>
+          <t>CL-04116</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ET-01571</t>
+          <t>ET-00032</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P-036804</t>
+          <t>P-040812</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PR-01190</t>
+          <t>PR-00456</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BR-00200</t>
+          <t>BR-00029</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>E-005499</t>
+          <t>E-000909</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45840</v>
+        <v>45844</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2092,50 +2092,50 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C-003039</t>
+          <t>C-003487</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CL-03595</t>
+          <t>CL-07493</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ET-03039</t>
+          <t>ET-03487</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P-002517</t>
+          <t>P-006200</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PR-01462</t>
+          <t>PR-00081</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BR-00104</t>
+          <t>BR-00389</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>E-002845</t>
+          <t>E-010361</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45799</v>
+        <v>45852</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2147,45 +2147,45 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C-000237</t>
+          <t>C-002526</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CL-03537</t>
+          <t>CL-07518</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ET-00237</t>
+          <t>ET-02526</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P-009506</t>
+          <t>P-043484</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PR-00877</t>
+          <t>PR-00503</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BR-00116</t>
+          <t>BR-00393</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>E-003091</t>
+          <t>E-010494</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45813</v>
+        <v>45730</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2202,50 +2202,50 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C-002840</t>
+          <t>C-003483</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CL-01856</t>
+          <t>CL-07905</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ET-02840</t>
+          <t>ET-03483</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P-048523</t>
+          <t>P-046782</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PR-00550</t>
+          <t>PR-00558</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BR-00039</t>
+          <t>BR-00271</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>E-001099</t>
+          <t>E-007260</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45857</v>
+        <v>45735</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2257,45 +2257,45 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C-002957</t>
+          <t>C-003483</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CL-05874</t>
+          <t>CL-07905</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ET-02957</t>
+          <t>ET-03483</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P-050764</t>
+          <t>P-005752</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PR-00604</t>
+          <t>PR-00094</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BR-00015</t>
+          <t>BR-00271</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>E-000697</t>
+          <t>E-007260</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45840</v>
+        <v>45733</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2312,50 +2312,50 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C-000607</t>
+          <t>C-002700</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CL-08227</t>
+          <t>CL-07848</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ET-00607</t>
+          <t>ET-02700</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P-048515</t>
+          <t>P-008986</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PR-01348</t>
+          <t>PR-00112</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BR-00440</t>
+          <t>BR-00446</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>E-011605</t>
+          <t>E-011731</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45875</v>
+        <v>45893</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2367,45 +2367,45 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C-000005</t>
+          <t>C-000717</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CL-06429</t>
+          <t>CL-07218</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ET-00005</t>
+          <t>ET-00717</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P-003267</t>
+          <t>P-028378</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PR-00009</t>
+          <t>PR-01285</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BR-00026</t>
+          <t>BR-00257</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>E-000883</t>
+          <t>E-006830</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45790</v>
+        <v>45772</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2422,50 +2422,50 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C-004178</t>
+          <t>C-003861</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CL-01309</t>
+          <t>CL-00018</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ET-04178</t>
+          <t>ET-03861</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P-004062</t>
+          <t>P-028122</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PR-00782</t>
+          <t>PR-01007</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BR-00405</t>
+          <t>BR-00253</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>E-010662</t>
+          <t>E-006805</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45862</v>
+        <v>45866</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2477,50 +2477,50 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C-000735</t>
+          <t>C-000195</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CL-01400</t>
+          <t>CL-06754</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ET-00735</t>
+          <t>ET-00195</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P-000610</t>
+          <t>P-009988</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PR-00040</t>
+          <t>PR-00132</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>BR-00487</t>
+          <t>BR-00086</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>E-012693</t>
+          <t>E-002580</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45893</v>
+        <v>45741</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -2532,45 +2532,45 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>C-003626</t>
+          <t>C-001395</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CL-09086</t>
+          <t>CL-03569</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ET-03626</t>
+          <t>ET-01395</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P-005172</t>
+          <t>P-021851</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PR-00081</t>
+          <t>PR-00242</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>BR-00382</t>
+          <t>BR-00008</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>E-009908</t>
+          <t>E-000532</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45772</v>
+        <v>45889</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2587,45 +2587,45 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C-001017</t>
+          <t>C-003291</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CL-08592</t>
+          <t>CL-07673</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ET-01017</t>
+          <t>ET-03291</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P-003518</t>
+          <t>P-021859</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PR-00044</t>
+          <t>PR-00244</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BR-00030</t>
+          <t>BR-00196</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>E-000911</t>
+          <t>E-005335</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45875</v>
+        <v>45719</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2642,45 +2642,45 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C-002118</t>
+          <t>C-002361</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CL-02315</t>
+          <t>CL-01805</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ET-02118</t>
+          <t>ET-02361</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P-038665</t>
+          <t>P-018469</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PR-00977</t>
+          <t>PR-00203</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>BR-00106</t>
+          <t>BR-00163</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>E-002862</t>
+          <t>E-004589</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45865</v>
+        <v>45743</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2697,50 +2697,50 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C-004771</t>
+          <t>C-003048</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CL-07063</t>
+          <t>CL-08573</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ET-04771</t>
+          <t>ET-03048</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P-005448</t>
+          <t>P-003220</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PR-00093</t>
+          <t>PR-00047</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>BR-00046</t>
+          <t>BR-00026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>E-001480</t>
+          <t>E-000885</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45784</v>
+        <v>45841</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2752,50 +2752,50 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C-000744</t>
+          <t>C-002741</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CL-02717</t>
+          <t>CL-08112</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ET-00744</t>
+          <t>ET-02741</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P-034534</t>
+          <t>P-017987</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PR-00386</t>
+          <t>PR-00974</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BR-00312</t>
+          <t>BR-00160</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>E-008331</t>
+          <t>E-004442</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45887</v>
+        <v>45886</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -2807,50 +2807,50 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C-001527</t>
+          <t>C-000968</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CL-01567</t>
+          <t>CL-06051</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ET-01527</t>
+          <t>ET-00968</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P-052726</t>
+          <t>P-027986</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PR-01012</t>
+          <t>PR-01070</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BR-00479</t>
+          <t>BR-00123</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>E-012600</t>
+          <t>E-003522</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45743</v>
+        <v>45799</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2862,50 +2862,50 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C-004331</t>
+          <t>C-004554</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CL-03443</t>
+          <t>CL-07764</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ET-04331</t>
+          <t>ET-04554</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P-046268</t>
+          <t>P-025780</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PR-01121</t>
+          <t>PR-00315</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BR-00421</t>
+          <t>BR-00233</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>E-011086</t>
+          <t>E-006285</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45865</v>
+        <v>45758</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2917,50 +2917,50 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C-002264</t>
+          <t>C-002948</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CL-07298</t>
+          <t>CL-02664</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ET-02264</t>
+          <t>ET-02948</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P-053760</t>
+          <t>P-015521</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PR-00608</t>
+          <t>PR-01057</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BR-00492</t>
+          <t>BR-00137</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>E-012722</t>
+          <t>E-003798</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45762</v>
+        <v>45801</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -2972,50 +2972,50 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C-000855</t>
+          <t>C-001307</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CL-06021</t>
+          <t>CL-06214</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ET-00855</t>
+          <t>ET-01307</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P-009161</t>
+          <t>P-041664</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PR-00140</t>
+          <t>PR-00510</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BR-00259</t>
+          <t>BR-00313</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>E-006787</t>
+          <t>E-008432</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45821</v>
+        <v>45862</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3027,45 +3027,45 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C-003229</t>
+          <t>C-004524</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CL-00032</t>
+          <t>CL-00607</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ET-03229</t>
+          <t>ET-04524</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P-021680</t>
+          <t>P-033315</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PR-00271</t>
+          <t>PR-00386</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>BR-00003</t>
+          <t>BR-00305</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>E-000294</t>
+          <t>E-007949</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45843</v>
+        <v>45824</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3082,50 +3082,50 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C-002732</t>
+          <t>C-003967</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CL-05084</t>
+          <t>CL-05022</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ET-02732</t>
+          <t>ET-03967</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P-037799</t>
+          <t>P-026437</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PR-01204</t>
+          <t>PR-00292</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BR-00344</t>
+          <t>BR-00161</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>E-008958</t>
+          <t>E-004483</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45840</v>
+        <v>45814</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3137,45 +3137,45 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C-000234</t>
+          <t>C-002538</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CL-06620</t>
+          <t>CL-07078</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ET-00234</t>
+          <t>ET-02538</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P-010966</t>
+          <t>P-023431</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PR-01286</t>
+          <t>PR-01460</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>BR-00042</t>
+          <t>BR-00210</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>E-001295</t>
+          <t>E-005710</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45829</v>
+        <v>45744</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3192,45 +3192,45 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C-004613</t>
+          <t>C-003239</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CL-01977</t>
+          <t>CL-06634</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ET-04613</t>
+          <t>ET-03239</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P-005331</t>
+          <t>P-030293</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PR-00799</t>
+          <t>PR-00345</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>BR-00393</t>
+          <t>BR-00273</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>E-010450</t>
+          <t>E-007366</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45878</v>
+        <v>45869</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3247,45 +3247,45 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C-003618</t>
+          <t>C-003038</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CL-04346</t>
+          <t>CL-01571</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ET-03618</t>
+          <t>ET-03038</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P-009112</t>
+          <t>P-023372</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PR-00135</t>
+          <t>PR-00271</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BR-00119</t>
+          <t>BR-00209</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>E-003332</t>
+          <t>E-005698</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45721</v>
+        <v>45761</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3302,50 +3302,50 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C-003056</t>
+          <t>C-003881</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CL-07675</t>
+          <t>CL-02638</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ET-03056</t>
+          <t>ET-03881</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P-024948</t>
+          <t>P-039938</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PR-00269</t>
+          <t>PR-00435</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>BR-00291</t>
+          <t>BR-00361</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>E-007719</t>
+          <t>E-009635</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45748</v>
+        <v>45800</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3357,50 +3357,50 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C-003601</t>
+          <t>C-002150</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CL-05671</t>
+          <t>CL-01625</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ET-03601</t>
+          <t>ET-02150</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P-027983</t>
+          <t>P-009364</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PR-01087</t>
+          <t>PR-00104</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>BR-00098</t>
+          <t>BR-00082</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>E-002777</t>
+          <t>E-002399</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45851</v>
+        <v>45868</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -3412,45 +3412,45 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C-004614</t>
+          <t>C-003196</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CL-08956</t>
+          <t>CL-09902</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ET-04614</t>
+          <t>ET-03196</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P-046490</t>
+          <t>P-033337</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PR-00534</t>
+          <t>PR-00390</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>BR-00318</t>
+          <t>BR-00305</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>E-008506</t>
+          <t>E-007879</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45878</v>
+        <v>45840</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3467,45 +3467,45 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C-003679</t>
+          <t>C-001809</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CL-03137</t>
+          <t>CL-06016</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ET-03679</t>
+          <t>ET-01809</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P-000373</t>
+          <t>P-019787</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PR-00760</t>
+          <t>PR-00651</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>BR-00002</t>
+          <t>BR-00176</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>E-000154</t>
+          <t>E-004809</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45729</v>
+        <v>45721</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3522,50 +3522,50 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C-003364</t>
+          <t>C-003415</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CL-05676</t>
+          <t>CL-06834</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ET-03364</t>
+          <t>ET-03415</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P-033423</t>
+          <t>P-041707</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PR-00899</t>
+          <t>PR-00472</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>BR-00305</t>
+          <t>BR-00381</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>E-007882</t>
+          <t>E-009863</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45881</v>
+        <v>45768</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3577,50 +3577,50 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C-002972</t>
+          <t>C-003683</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CL-00551</t>
+          <t>CL-04288</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ET-02972</t>
+          <t>ET-03683</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P-009162</t>
+          <t>P-029154</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PR-00140</t>
+          <t>PR-00362</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>BR-00081</t>
+          <t>BR-00079</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>E-002317</t>
+          <t>E-002235</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45752</v>
+        <v>45865</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3632,50 +3632,50 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C-003903</t>
+          <t>C-004826</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CL-08594</t>
+          <t>CL-01031</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ET-03903</t>
+          <t>ET-04826</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P-011610</t>
+          <t>P-053345</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PR-00141</t>
+          <t>PR-01265</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BR-00087</t>
+          <t>BR-00486</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>E-002571</t>
+          <t>E-012730</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45739</v>
+        <v>45817</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -3687,50 +3687,50 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C-002968</t>
+          <t>C-001612</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CL-01679</t>
+          <t>CL-03663</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ET-02968</t>
+          <t>ET-01612</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P-052446</t>
+          <t>P-002743</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PR-00570</t>
+          <t>PR-00034</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>BR-00275</t>
+          <t>BR-00460</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>E-007378</t>
+          <t>E-012165</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45852</v>
+        <v>45767</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3742,45 +3742,45 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C-004674</t>
+          <t>C-002225</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CL-04042</t>
+          <t>CL-08765</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ET-04674</t>
+          <t>ET-02225</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P-031790</t>
+          <t>P-042422</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PR-00374</t>
+          <t>PR-01362</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BR-00287</t>
+          <t>BR-00385</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>E-007653</t>
+          <t>E-010211</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45745</v>
+        <v>45839</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3797,50 +3797,50 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C-004678</t>
+          <t>C-004165</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CL-06524</t>
+          <t>CL-00047</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ET-04678</t>
+          <t>ET-04165</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P-018134</t>
+          <t>P-013994</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PR-00197</t>
+          <t>PR-01238</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BR-00095</t>
+          <t>BR-00231</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>E-002713</t>
+          <t>E-006169</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45851</v>
+        <v>45808</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Cliente no lo reconoce</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -3852,50 +3852,50 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C-003306</t>
+          <t>C-001178</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CL-08782</t>
+          <t>CL-09255</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ET-03306</t>
+          <t>ET-01178</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P-052458</t>
+          <t>P-045033</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PR-01033</t>
+          <t>PR-00503</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BR-00350</t>
+          <t>BR-00409</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>E-009320</t>
+          <t>E-010745</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45812</v>
+        <v>45748</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Recibí otro artículo</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -3907,45 +3907,45 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C-002377</t>
+          <t>C-000202</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CL-03495</t>
+          <t>CL-06328</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ET-02377</t>
+          <t>ET-00202</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P-011187</t>
+          <t>P-006847</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PR-00137</t>
+          <t>PR-00815</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>BR-00122</t>
+          <t>BR-00058</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>E-003471</t>
+          <t>E-001771</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45716</v>
+        <v>45821</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3962,50 +3962,50 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C-001897</t>
+          <t>C-001036</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CL-01589</t>
+          <t>CL-08775</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ET-01897</t>
+          <t>ET-01036</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P-042499</t>
+          <t>P-036144</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PR-00504</t>
+          <t>PR-00390</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>BR-00386</t>
+          <t>BR-00326</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>E-010220</t>
+          <t>E-008719</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45716</v>
+        <v>45773</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4017,50 +4017,50 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C-002246</t>
+          <t>C-002702</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CL-02914</t>
+          <t>CL-08734</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ET-02246</t>
+          <t>ET-02702</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P-017128</t>
+          <t>P-040485</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PR-00211</t>
+          <t>PR-00456</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BR-00154</t>
+          <t>BR-00435</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>E-004118</t>
+          <t>E-011564</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45804</v>
+        <v>45765</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4072,50 +4072,50 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C-004882</t>
+          <t>C-002978</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CL-01033</t>
+          <t>CL-06384</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ET-04882</t>
+          <t>ET-02978</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P-022180</t>
+          <t>P-012553</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PR-00246</t>
+          <t>PR-01108</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>BR-00247</t>
+          <t>BR-00463</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>E-006632</t>
+          <t>E-012284</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45818</v>
+        <v>45747</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4127,50 +4127,50 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C-003408</t>
+          <t>C-002038</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CL-02660</t>
+          <t>CL-09739</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ET-03408</t>
+          <t>ET-02038</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P-046998</t>
+          <t>P-006848</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PR-00552</t>
+          <t>PR-01364</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BR-00426</t>
+          <t>BR-00253</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>E-011304</t>
+          <t>E-006807</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45723</v>
+        <v>45810</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4182,50 +4182,50 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C-001272</t>
+          <t>C-002618</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CL-09838</t>
+          <t>CL-09904</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ET-01272</t>
+          <t>ET-02618</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P-038123</t>
+          <t>P-039319</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PR-00465</t>
+          <t>PR-00429</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BR-00346</t>
+          <t>BR-00355</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>E-009110</t>
+          <t>E-009540</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45723</v>
+        <v>45849</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4237,50 +4237,50 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C-001046</t>
+          <t>C-003694</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CL-08784</t>
+          <t>CL-08597</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ET-01046</t>
+          <t>ET-03694</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P-015489</t>
+          <t>P-019844</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PR-00178</t>
+          <t>PR-00809</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BR-00137</t>
+          <t>BR-00177</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>E-003784</t>
+          <t>E-004829</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45715</v>
+        <v>45765</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4292,50 +4292,50 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>C-004149</t>
+          <t>C-003659</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CL-05070</t>
+          <t>CL-06294</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ET-04149</t>
+          <t>ET-03659</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P-031634</t>
+          <t>P-007985</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PR-00775</t>
+          <t>PR-00091</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BR-00360</t>
+          <t>BR-00072</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>E-009553</t>
+          <t>E-001922</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45796</v>
+        <v>45799</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -4347,50 +4347,50 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C-002076</t>
+          <t>C-001030</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CL-07652</t>
+          <t>CL-04639</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ET-02076</t>
+          <t>ET-01030</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P-014327</t>
+          <t>P-009849</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PR-00186</t>
+          <t>PR-00133</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>BR-00464</t>
+          <t>BR-00256</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>E-012277</t>
+          <t>E-006825</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45830</v>
+        <v>45888</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C-003158</t>
+          <t>C-003410</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CL-06712</t>
+          <t>CL-04398</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ET-03158</t>
+          <t>ET-03410</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P-014867</t>
+          <t>P-023813</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PR-00824</t>
+          <t>PR-00677</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>BR-00199</t>
+          <t>BR-00213</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>E-005449</t>
+          <t>E-005763</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45881</v>
+        <v>45856</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Calidad inferior a lo esperado</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4457,45 +4457,45 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C-004506</t>
+          <t>C-003692</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CL-03106</t>
+          <t>CL-05035</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ET-04506</t>
+          <t>ET-03692</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P-004751</t>
+          <t>P-032096</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PR-00055</t>
+          <t>PR-00363</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>BR-00041</t>
+          <t>BR-00169</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>E-001273</t>
+          <t>E-004685</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45839</v>
+        <v>45752</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Llegó dañado</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4512,45 +4512,45 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C-002824</t>
+          <t>C-000479</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CL-07038</t>
+          <t>CL-00469</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ET-02824</t>
+          <t>ET-00479</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P-051727</t>
+          <t>P-016314</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PR-01353</t>
+          <t>PR-00178</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>BR-00468</t>
+          <t>BR-00147</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>E-012421</t>
+          <t>E-003893</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45884</v>
+        <v>45750</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4567,50 +4567,50 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C-000792</t>
+          <t>C-000778</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CL-00106</t>
+          <t>CL-09677</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ET-00792</t>
+          <t>ET-00778</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P-050285</t>
+          <t>P-038513</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PR-00801</t>
+          <t>PR-00429</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BR-00458</t>
+          <t>BR-00349</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>E-011948</t>
+          <t>E-009317</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45852</v>
+        <v>45854</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4622,50 +4622,50 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C-003463</t>
+          <t>C-000869</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CL-04517</t>
+          <t>CL-07386</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ET-03463</t>
+          <t>ET-00869</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P-039628</t>
+          <t>P-043109</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PR-00434</t>
+          <t>PR-00826</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>BR-00251</t>
+          <t>BR-00129</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>E-006701</t>
+          <t>E-003661</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45730</v>
+        <v>45741</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4677,50 +4677,50 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C-000278</t>
+          <t>C-001357</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CL-08191</t>
+          <t>CL-08076</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ET-00278</t>
+          <t>ET-01357</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P-024117</t>
+          <t>P-020353</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PR-00270</t>
+          <t>PR-00196</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>BR-00349</t>
+          <t>BR-00183</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>E-009266</t>
+          <t>E-004871</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45822</v>
+        <v>45862</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Error en el pedido</t>
+          <t>Cambio de opinión</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4732,50 +4732,50 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C-004203</t>
+          <t>C-000893</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CL-03762</t>
+          <t>CL-00572</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ET-04203</t>
+          <t>ET-00893</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P-043587</t>
+          <t>P-018346</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PR-01246</t>
+          <t>PR-00205</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>BR-00394</t>
+          <t>BR-00129</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>E-010480</t>
+          <t>E-003664</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45797</v>
+        <v>45810</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4787,50 +4787,50 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C-004977</t>
+          <t>C-001513</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CL-03169</t>
+          <t>CL-07332</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ET-04977</t>
+          <t>ET-01513</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P-016427</t>
+          <t>P-022539</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PR-00186</t>
+          <t>PR-00764</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BR-00170</t>
+          <t>BR-00312</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>E-004674</t>
+          <t>E-008391</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45769</v>
+        <v>45750</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Vencido o caducado</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -4842,45 +4842,45 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C-000078</t>
+          <t>C-001220</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CL-03328</t>
+          <t>CL-01962</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ET-00078</t>
+          <t>ET-01220</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P-041748</t>
+          <t>P-041487</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PR-01355</t>
+          <t>PR-00469</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BR-00281</t>
+          <t>BR-00171</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>E-007543</t>
+          <t>E-004721</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45752</v>
+        <v>45759</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4897,50 +4897,50 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>C-002885</t>
+          <t>C-004205</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CL-06468</t>
+          <t>CL-08258</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ET-02885</t>
+          <t>ET-04205</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P-049132</t>
+          <t>P-012876</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PR-00732</t>
+          <t>PR-00154</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>BR-00199</t>
+          <t>BR-00321</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>E-005426</t>
+          <t>E-008628</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45875</v>
+        <v>45863</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -4952,50 +4952,50 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>C-004344</t>
+          <t>C-002488</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CL-07427</t>
+          <t>CL-05677</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ET-04344</t>
+          <t>ET-02488</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P-028101</t>
+          <t>P-021690</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PR-00689</t>
+          <t>PR-00242</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>BR-00253</t>
+          <t>BR-00195</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>E-006739</t>
+          <t>E-005314</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45858</v>
+        <v>45884</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -5007,50 +5007,50 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>C-001132</t>
+          <t>C-003147</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CL-05612</t>
+          <t>CL-08087</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ET-01132</t>
+          <t>ET-03147</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P-037100</t>
+          <t>P-029192</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PR-00420</t>
+          <t>PR-01172</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BR-00006</t>
+          <t>BR-00267</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>E-000455</t>
+          <t>E-006905</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45849</v>
+        <v>45893</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Retraso en la entrega</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5062,50 +5062,50 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C-004235</t>
+          <t>C-004721</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CL-09557</t>
+          <t>CL-08120</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ET-04235</t>
+          <t>ET-04721</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P-010604</t>
+          <t>P-028169</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PR-01345</t>
+          <t>PR-00328</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>BR-00276</t>
+          <t>BR-00273</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>E-007458</t>
+          <t>E-007376</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45761</v>
+        <v>45861</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Calidad inferior a lo esperado</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5117,50 +5117,50 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C-003277</t>
+          <t>C-000437</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CL-01508</t>
+          <t>CL-04214</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ET-03277</t>
+          <t>ET-00437</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P-027329</t>
+          <t>P-027649</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PR-00319</t>
+          <t>PR-00294</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>BR-00328</t>
+          <t>BR-00193</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>E-008679</t>
+          <t>E-005201</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45868</v>
+        <v>45843</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Vencido o caducado</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5172,45 +5172,45 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>C-004705</t>
+          <t>C-004819</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CL-00819</t>
+          <t>CL-07152</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ET-04705</t>
+          <t>ET-04819</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P-048272</t>
+          <t>P-011550</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PR-00528</t>
+          <t>PR-00102</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BR-00437</t>
+          <t>BR-00427</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>E-011547</t>
+          <t>E-011385</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45859</v>
+        <v>45799</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5227,50 +5227,50 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C-001830</t>
+          <t>C-004753</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CL-08444</t>
+          <t>CL-06068</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ET-01830</t>
+          <t>ET-04753</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P-053898</t>
+          <t>P-026374</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PR-00987</t>
+          <t>PR-01175</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>BR-00235</t>
+          <t>BR-00381</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>E-006334</t>
+          <t>E-009832</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45730</v>
+        <v>45799</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>No funciona correctamente</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5282,45 +5282,45 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>C-002470</t>
+          <t>C-000971</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CL-04802</t>
+          <t>CL-00683</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ET-02470</t>
+          <t>ET-00971</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P-021803</t>
+          <t>P-043461</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PR-01196</t>
+          <t>PR-00514</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>BR-00454</t>
+          <t>BR-00393</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>E-011735</t>
+          <t>E-010494</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45778</v>
+        <v>45725</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Cambio de opinión</t>
+          <t>Pedido duplicado</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5337,50 +5337,50 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C-001652</t>
+          <t>C-004487</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CL-09032</t>
+          <t>CL-04543</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ET-01652</t>
+          <t>ET-04487</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P-022659</t>
+          <t>P-044969</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PR-00279</t>
+          <t>PR-01150</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BR-00202</t>
+          <t>BR-00408</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>E-005522</t>
+          <t>E-010741</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45759</v>
+        <v>45782</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>No funciona correctamente</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -5392,41 +5392,41 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>C-002064</t>
+          <t>C-000796</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CL-07474</t>
+          <t>CL-03782</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ET-02064</t>
+          <t>ET-00796</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P-006442</t>
+          <t>P-005608</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PR-00059</t>
+          <t>PR-01084</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>BR-00094</t>
+          <t>BR-00468</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>E-002703</t>
+          <t>E-012458</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>45872</v>
+        <v>45828</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -5447,45 +5447,45 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C-000971</t>
+          <t>C-003007</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CL-02536</t>
+          <t>CL-08825</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ET-00971</t>
+          <t>ET-03007</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P-022376</t>
+          <t>P-048124</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PR-00276</t>
+          <t>PR-00783</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>BR-00271</t>
+          <t>BR-00187</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>E-007230</t>
+          <t>E-004898</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45803</v>
+        <v>45796</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Tamaño incorrecto</t>
+          <t>No coincide con la descripción</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5502,50 +5502,50 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C-000261</t>
+          <t>C-003808</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CL-07468</t>
+          <t>CL-05250</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ET-00261</t>
+          <t>ET-03808</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P-022454</t>
+          <t>P-004261</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PR-00272</t>
+          <t>PR-00054</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>BR-00200</t>
+          <t>BR-00191</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>E-005491</t>
+          <t>E-004925</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>45829</v>
+        <v>45792</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>No coincide con la descripción</t>
+          <t>Cliente no lo reconoce</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -5557,45 +5557,45 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>C-002449</t>
+          <t>C-002740</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CL-02843</t>
+          <t>CL-06425</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ET-02449</t>
+          <t>ET-02740</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P-047421</t>
+          <t>P-046141</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PR-00562</t>
+          <t>PR-00520</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>BR-00345</t>
+          <t>BR-00420</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>E-009079</t>
+          <t>E-011004</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45874</v>
+        <v>45884</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Producto defectuoso</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5612,45 +5612,45 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C-002484</t>
+          <t>C-003669</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CL-03620</t>
+          <t>CL-08441</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ET-02484</t>
+          <t>ET-03669</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P-021291</t>
+          <t>P-010380</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PR-01277</t>
+          <t>PR-00141</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BR-00068</t>
+          <t>BR-00090</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>E-001874</t>
+          <t>E-002641</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>45869</v>
+        <v>45795</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Pedido duplicado</t>
+          <t>Retraso en la entrega</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5667,50 +5667,50 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C-004684</t>
+          <t>C-002421</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CL-08829</t>
+          <t>CL-09901</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ET-04684</t>
+          <t>ET-02421</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P-041320</t>
+          <t>P-005729</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PR-01257</t>
+          <t>PR-00067</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BR-00378</t>
+          <t>BR-00093</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>E-009759</t>
+          <t>E-002694</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>45768</v>
+        <v>45798</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Recibí otro artículo</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5722,50 +5722,50 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>C-002120</t>
+          <t>C-002169</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CL-04570</t>
+          <t>CL-03074</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ET-02120</t>
+          <t>ET-02169</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P-002496</t>
+          <t>P-046526</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PR-00782</t>
+          <t>PR-00647</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>BR-00277</t>
+          <t>BR-00309</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>E-007479</t>
+          <t>E-008279</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>45831</v>
+        <v>45720</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Producto incompleto</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
@@ -5777,45 +5777,45 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>C-003056</t>
+          <t>C-000130</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CL-07675</t>
+          <t>CL-07071</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ET-03056</t>
+          <t>ET-00130</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P-032202</t>
+          <t>P-045181</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PR-00364</t>
+          <t>PR-00503</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>BR-00291</t>
+          <t>BR-00293</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>E-007719</t>
+          <t>E-007786</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45719</v>
+        <v>45729</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Producto defectuoso</t>
+          <t>Error en el pedido</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5832,50 +5832,50 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C-003812</t>
+          <t>C-000451</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CL-08437</t>
+          <t>CL-05765</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ET-03812</t>
+          <t>ET-00451</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P-021686</t>
+          <t>P-027763</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PR-00241</t>
+          <t>PR-00326</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BR-00374</t>
+          <t>BR-00250</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>E-009732</t>
+          <t>E-006759</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>45878</v>
+        <v>45825</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Tamaño incorrecto</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Rechazada</t>
+          <t>Procesada</t>
         </is>
       </c>
     </row>
@@ -5887,50 +5887,50 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>C-002413</t>
+          <t>C-000129</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CL-04173</t>
+          <t>CL-04080</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ET-02413</t>
+          <t>ET-00129</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P-002801</t>
+          <t>P-015756</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PR-00782</t>
+          <t>PR-00186</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>BR-00055</t>
+          <t>BR-00364</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>E-001703</t>
+          <t>E-009699</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>45772</v>
+        <v>45887</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Problema con el embalaje</t>
+          <t>Llegó dañado</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Procesada</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
@@ -5942,50 +5942,50 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>C-002392</t>
+          <t>C-002859</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CL-06916</t>
+          <t>CL-08867</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ET-02392</t>
+          <t>ET-02859</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P-007654</t>
+          <t>P-005387</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PR-00864</t>
+          <t>PR-00085</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BR-00344</t>
+          <t>BR-00139</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>E-008976</t>
+          <t>E-003836</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>45886</v>
+        <v>45773</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Producto incompleto</t>
+          <t>Problema con el embalaje</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
     </row>
